--- a/planilhas/ipca-defasagem.xlsx
+++ b/planilhas/ipca-defasagem.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modelo mensal" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por ponto" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidade" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contrafactual Bahia" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidade" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -695,39 +696,98 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Contrafactual Bahia | A segunda estimativa, por grupo de controle</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Sensibilidade | O mesmo cálculo com a margem escalando junto</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-    </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>ATENÇÃO — a tabela mais recente da Petrobras é de 01/09/2026.</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Depois dessa data o preço segue valendo até mudar. Reajuste que ainda não apareceu não está aqui.</t>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>DUAS ESTIMATIVAS, E ELAS NÃO BATEM</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A contábil supõe que R$ 1,00 na refinaria vira R$ 0,70 na bomba, porque 70% do litro é gasolina A.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Fontes: PPI e preços de revenda da ANP; tabela de preços da Petrobras; IPCA da tabela 7060 do</t>
+          <t>A da Bahia MEDE quanto aparece, usando a Acelen (que segue o PPI) como controle, e acha R$ 0,26.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
+        <is>
+          <t>A contábil é teto e a da Bahia é piso. O teto supõe repasse integral e imediato; o piso subestima</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>porque a Acelen não atende a Bahia inteira, não segue o PPI perfeitamente e também recebeu as</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>subvenções de 2026, que encolhem o próprio spread que serve de medida. A verdade mora no meio,</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>e a largura entre as duas é a sua incerteza honesta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>ATENÇÃO — a tabela mais recente da Petrobras é de 01/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Depois dessa data o preço segue valendo até mudar. Reajuste que ainda não apareceu não está aqui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Fontes: PPI e preços de revenda da ANP; tabela de preços da Petrobras; IPCA da tabela 7060 do</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>SIDRA (IBGE); teor de anidro pela legislação (CNPE e MAPA).</t>
         </is>
@@ -7427,6 +7487,2991 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Segunda estimativa: a Bahia como grupo de controle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Na Bahia quem domina é a Acelen, que segue o PPI. O preço de bomba baiano é, então, uma leitura de</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mercado do que o preço seria sem defasagem. O excesso do spread BA − Brasil mede o represamento SEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>nenhuma hipótese sobre mistura, tributo ou margem: é um caminho que não divide suposição nenhuma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>com o modelo contábil, e por isso serve de segunda opinião.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Estimado de 2023-06 em diante, quando o ICMS virou monofásico e passou a ser o mesmo valor por litro em</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>todo estado. Antes disso o spread carregava diferença de alíquota: o R² era 0,13, contra 0.71 agora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>spread BA − Brasil = R$ 0.189 estrutural -0.262 × defasagem   (R² 0.71, n=40 meses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Leia a inclinação assim: a cada R$ 1,00 de defasagem na refinaria, R$ 0.262 aparecem como</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>diferença de preço entre a Bahia e o Brasil. O contábil supõe R$ 0,70 (o teor de gasolina A).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A distância entre os dois é o tamanho da sua incerteza, e as razões estão no LEIA-ME.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>mês</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>defasagem R$/l</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>bomba BA R$/l</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>bomba Brasil R$/l</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>spread observado R$/l</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>spread estrutural R$/l</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>excesso atribuído R$/l</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>falta no preço %</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>peso do item %</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>nível represado (Bahia) p.p.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>nível represado (contábil) p.p.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>0.04965360000000003</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>4.724175</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>4.6086</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.1155749999999998</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-0.01299053788340219</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>-0.2818760118778412</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>5.1495</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>-0.01451520523164943</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>-0.04050136389272234</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-0.04668699999999998</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>4.6354</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>4.59286</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.0425399999999998</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0.01221440624974619</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0.2659433609939382</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>5.185</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0.01378916326753569</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.03847550967153363</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0.3915765</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>4.62335</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>4.525225</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.09812500000000046</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-0.1024455297803187</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>-2.263877039933235</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>5.1344</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>-0.116236502738332</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>-0.3243314041993494</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.2114314999999999</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>4.35075</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>4.181575</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.1691749999999992</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-0.05531540332412045</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>-1.322836570529536</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>5.0428</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>-0.06670800257866345</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>-0.1861334403391066</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-0.2692482</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>3.95078</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3.87496</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.07582000000000022</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0.07044159823533132</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>1.817866461468797</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>4.5878</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0.08340007751926548</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0.2327088618026509</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-0.1755875000000001</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>4.1654</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>3.97485</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.19055</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0.04593777834037977</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>1.155710991367719</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>4.4052</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0.05091138059173075</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0.1420565757575759</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>-0.1044136000000002</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>4.36225</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>4.13645</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.2258000000000004</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0.02731702890308868</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0.6603978992394125</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>4.536</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0.02995564870949975</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0.08358439372118619</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>-0.35370925</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>4.723775</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>4.52632</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.1974549999999997</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0.09253857548767407</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>2.044454998490475</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>4.9164</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>0.1005135855457857</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.2804601960071318</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-0.2546565000000002</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>5.11405</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>4.89085</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.2231999999999994</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0.06662406976542708</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>1.362218627956839</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>5.0107</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0.06825668879103335</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0.1904546953845448</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>-0.1719144999999999</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>5.693875</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>5.463475</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.2304000000000004</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.04497683601906292</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>0.8232276347757228</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>5.3202</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0.04379735662533801</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0.1222065172288699</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>-0.1373274</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>5.57775</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>5.45035</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.1273999999999997</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0.0359280453407029</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0.6591878565725667</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>5.8624</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0.03864422890371015</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.1078278916628841</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>-0.06494299999999986</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>5.664800000000001</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>5.558</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.1068000000000007</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0.01699060091839838</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0.3056963101547028</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>5.8183</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0.01778632841373107</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0.04962868577491895</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>-0.03834925</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>5.9039</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>5.665</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.2389000000000001</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0.01003305671542569</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0.1771060320463493</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>5.9363</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>0.01051354538036743</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0.02933564634170345</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>-0.1973295999999997</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>5.99204</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>5.77808</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0.2139600000000002</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0.05162601793861059</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0.8934804976499215</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>5.9454</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0.05312098950727843</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0.1482219846044359</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>-0.09127399999999986</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>6.113225</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>5.908675000000001</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.2045499999999993</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.02387940360355843</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0.4041414293992888</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>5.9796</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0.02416604091235987</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.06742981592184363</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-0.07488725000000007</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>6.19525</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>6.065425</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.1298249999999994</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.01959224825810839</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.3230152587511739</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>6.0939</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.01968422685303779</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.05492433775469161</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>-0.4351180000000001</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>6.27352</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>6.29028</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>-0.01676000000000055</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0.1138369999909411</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>1.80972866058333</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>6.1629</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0.11153176762309</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0.3112039157566914</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>-0.1939705000000003</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>6.771025</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>6.743325</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.02769999999999939</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.05074719916607186</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0.7525545508494973</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>6.2761</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0.0472310761658653</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0.1317875271007257</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>-0.0462904</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>6.813925</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>6.694375</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0.1195500000000003</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.01211064645539981</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0.1809077987922669</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>6.675</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0.01207559556938381</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0.03369419051068995</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>-0.2468485000000001</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>6.84066</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>6.632479999999999</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.2081800000000005</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.06458131516568798</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0.9737129273769086</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>6.5822</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0.06409173230580288</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0.1788333358850688</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>-0.3662380000000004</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>6.917225</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>6.607175</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.3100500000000004</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0.0958163882043085</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>1.450186928669341</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>6.4742</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>0.09388800213591043</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>0.2619730192567931</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>-0.5082165</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>7.425975</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>6.924225</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0.5017500000000004</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0.1329612696001914</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>1.920233233324905</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>6.3805</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>0.1225204814522955</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.3418654110925772</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>0.02847960000000027</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>7.2883</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>7.23156</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0.05673999999999957</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>-0.007450926472685651</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>-0.1030334598991871</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>6.7133</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>-0.006916945263412124</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>-0.01930015543484413</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>-0.7093084999999997</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>7.730525</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>7.2906</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.4399249999999997</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0.1855716189816886</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>2.54535455218622</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>6.8084</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>0.1732979193310466</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0.483548250311634</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>-0.7947427500000001</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>7.93085</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>7.2851</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0.6457500000000005</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.2079232080138042</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>2.854088591972714</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>6.8393</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>0.1951996810707898</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0.5446601125248454</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>-0.06823999999999986</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>6.788120000000001</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>6.27768</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0.5104400000000009</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0.01785317288501464</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>0.2843912541737495</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>6.7443</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>0.01918019935524019</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0.05351796417784904</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>0.05330499999999994</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>5.679475</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>5.4673</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0.2121750000000002</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>-0.01394582914178936</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>-0.255077079029674</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>5.744</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>-0.01465162741946447</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>-0.04088201883928078</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>0.2343575999999997</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>5.453333333333333</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>5.092866666666667</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0.3604666666666665</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>-0.06131340489034452</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>-1.203907522096485</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>5.0966</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>-0.06135835077116945</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>-0.1712064592116029</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>-0.1773995000000005</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>5.33188</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>4.84572</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0.4861599999999999</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0.04641183973058573</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0.9577903744043347</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>4.6857</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0.0448791835734639</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>0.1252251081613263</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>-0.1625212500000004</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>5.515175</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>5.00905</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.5061249999999999</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0.04251934310871481</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0.8488504428726966</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>4.5855</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>0.0389240370579275</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.108608632389126</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0.1713171999999998</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>5.20106</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>4.97152</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0.2295400000000001</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>-0.04482056843166227</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>-0.9015465779411985</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>4.7029</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>-0.04239883401399662</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>-0.1183042594040453</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>-0.1530252500000002</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>5.5367</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>5.035675</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.5010249999999994</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.04003496840595833</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.7950268515334751</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>4.6249</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>0.03676919685657169</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>0.1025960431261451</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>0.1762540000000002</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>5.4066</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>5.097775</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.3088249999999997</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>-0.04611215025901789</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>-0.9045544430465818</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>4.6404</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>-0.04197494437513358</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>-0.1171214922133678</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>0.07542239999999953</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>5.859475</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>5.463525</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.39595</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>-0.01973225595842208</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>-0.3611634605574621</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>4.6555</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>-0.01681396490625265</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>-0.04691552756434692</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>0.04910174999999939</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>5.83002</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>5.50016</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>-0.0128461610742491</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>-0.2335597705202958</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>5.0061</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>-0.01169223567201653</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>-0.03262451230377804</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>0.2591524999999996</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>5.5517</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>5.439299999999999</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0.1124000000000009</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>-0.06780032804929306</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>-1.246489953657512</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>4.9503</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>-0.06170499217590784</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>-0.1721736828539516</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>-0.04443919999999997</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>5.523175</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>5.36325</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0.1599250000000003</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0.01162632943246987</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0.2167776895067332</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>4.8435</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>0.01049962739125862</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>0.02929681137295482</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>-0.2336144999999998</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>5.86312</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>5.56742</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.2957000000000001</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0.06111899262816908</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>1.097797411155779</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>4.7924</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>0.05261084313222955</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>0.1467985376986108</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>-0.3583409999999999</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>6.074825</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>5.6569</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.4179249999999994</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0.09375034913231306</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>1.65727428684108</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>5.0125</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0.08307087362790913</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>0.2317902935574254</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>-0.1701287999999999</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>6.11738</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>5.84584</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.2715399999999999</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0.04450965532122045</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>0.7613902419707083</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>5.062</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>0.03854157404855725</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>0.1075414567432567</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>-0.04117499999999996</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>6.08525</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>5.776675</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0.3085750000000003</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0.01077233870956153</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>0.1864799163802971</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>5.1909</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>0.009679985979384843</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>0.02700978927756882</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>0.03454049999999997</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>5.92995</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>5.683199999999999</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0.2467500000000005</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>-0.009036599033336005</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>-0.1590054728557152</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>5.0988</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>-0.008107371049967206</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>-0.02262176661423141</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>0.04172339999999997</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>5.86862</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>5.64252</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0.2260999999999997</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>-0.01091581291838542</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>-0.1934563442998061</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>4.9999</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>-0.009672623758646004</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>-0.02698924668265242</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>0.0059840000000001</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>5.8371</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>5.612925</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0.2241749999999998</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>-0.001565553730127925</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>-0.0278919410134275</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>4.9556</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>-0.001382213028861413</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>-0.003856749661183852</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>-0.1855942500000001</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>6.010225</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>5.73435</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.2758750000000001</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0.04855577713532586</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>0.8467529386124992</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>4.9198</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>0.04165855107385773</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>0.1162386689929112</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>-0.3354034</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>5.91926</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>5.76526</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0.1539999999999999</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0.08774933889832549</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>1.522036107622648</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>5.0234</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>0.07645796183031611</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>0.2133384740460622</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>-0.5224365</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>6.113</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>5.817125</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0.2958749999999997</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0.1366815526955154</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>2.349640977209797</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>5.0258</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>0.11808825623261</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>0.3294982992528097</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>-0.2179826</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>6.27165</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>5.867875</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0.4037750000000004</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0.05702932361847891</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>0.971890567172595</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>5.0811</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>0.04938273160860673</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>0.1377912300224187</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>-0.3422657500000001</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>6.202859999999999</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>5.865</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.3378599999999992</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0.08954468943975989</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>1.526763673312189</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>5.0802</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>0.07756264813160582</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>0.2164208487808186</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>-0.4238147499999998</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>6.26765</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>6.01565</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.2519999999999998</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0.1108798066085766</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>1.84318912517478</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>5.1023</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>0.09404503873379279</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>0.2624111940048456</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>-0.1344591999999998</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>6.36198</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>6.1172</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.2447800000000004</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0.0351776574381706</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0.575061424151092</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>5.2433</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>0.03015219565251421</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>0.08413281306035431</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>0.1043535</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>6.26095</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>6.098025</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.1629250000000004</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>-0.02730130534373357</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>-0.4477073371088766</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>5.2801</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>-0.02363939510668579</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>-0.06596033112450343</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>-0.04135449999999996</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>6.27465</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>6.09905</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0.1756000000000002</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0.01081930008899969</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>0.1773932020396568</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>0.009313143107081983</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>0.02598619805543485</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>-0.1108155999999998</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>6.272119999999999</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>6.10504</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0.1670799999999995</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0.02899194116583572</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>0.4748853597328718</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>5.2148</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>0.0247643217393498</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>0.06909918187962724</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>-0.2341829999999998</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>6.3634</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>6.1435</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0.2199000000000009</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0.0612677254649969</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>0.9972772111173909</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>5.187</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>0.05172876894065907</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>0.1443373111955725</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>-0.2834567999999997</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>6.397625</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>6.168575</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0.22905</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0.07415889882522016</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>1.202204704088386</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>5.1882</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>0.06237278445751364</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>0.1740370046444761</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>-0.1788854999999997</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>6.536799999999999</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>6.330075</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0.2067249999999996</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0.04680061193027971</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>0.7393374001142121</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>5.2119</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>0.03853352595655262</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>0.1075190003812749</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>-0.08753250000000001</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>6.545699999999999</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>6.354979999999999</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0.1907199999999998</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0.02290054008730286</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>0.3603558168130012</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>5.2865</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>0.01905021025581931</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>0.05315525929467917</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>0.07261400000000018</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>6.453125</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>6.3236</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0.1295250000000001</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>-0.01899751312825995</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>-0.3004224354522732</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>5.2842</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>-0.01587492233416902</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>-0.04429534381112037</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>0.1597328000000002</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>6.36924</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>6.28504</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0.08419999999999916</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>-0.04178981966306382</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>-0.6649093667353561</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>5.2425</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>-0.03485787355110104</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>-0.09726293212453711</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>0.01465999999999978</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>6.4064</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>6.23115</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.1752500000000001</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>-0.003835397340186274</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>-0.06155199826976198</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>5.1928</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>-0.003196272166152201</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>-0.008918467223546087</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>0.1171537499999997</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>6.305375</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>6.21305</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0.09232499999999977</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>-0.03065014878191359</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>-0.4933188817394611</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>5.1632</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>-0.02547104050197186</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>-0.07107111912184821</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>0.1355179999999997</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>6.25964</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>6.18242</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0.07721999999999962</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>-0.03545466417103479</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>-0.5734755026516281</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>5.1244</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>-0.02938717865788003</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>-0.07862841855454643</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>0.1668764999999999</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>6.233000000000001</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>6.18995</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.04305000000000092</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>-0.04365877791538906</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>-0.7053171336664926</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>5.0824</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>-0.03584703800146582</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>-0.09591243653341296</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>0.2237595999999999</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>6.3306</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>6.218225</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0.1123750000000001</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>-0.05854072132886472</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>-0.9414378110934344</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>5.0963</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>-0.0479784951667547</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>-0.1283713977278081</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>0.1167457500000002</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>6.3212</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>6.18876</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0.1324399999999999</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>-0.03054340648213227</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>-0.493530311114541</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>5.1056</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>-0.02519768356426401</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>-0.06741899360130313</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>0.2733410000000003</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>6.32395</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>6.200324999999999</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0.1236250000000005</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>-0.07151237001117822</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>-1.153364864118869</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>5.0754</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>-0.05853788031348905</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>-0.1566241185712041</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>0.2821082</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>6.51366</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>6.30542</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0.20824</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>-0.07380607366471714</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>-1.170517961764912</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>5.0679</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>-0.05932067978428399</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>-0.1587185790551621</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>0.007392500000000024</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>6.5032</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>6.311825</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0.1913749999999999</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>-0.0019340501253293</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>-0.03064169436461404</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>5.1556</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>-0.001579763194662041</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>-0.004226818883603409</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>-1.049306</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>7.0772</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>6.566475000000001</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0.5107249999999999</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0.2745228814080189</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>4.180673518257801</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>5.0907</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0.2128255467939499</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>0.569436636542437</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>-1.53745325</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>7.4682</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>6.78135</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0.6868499999999997</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.4022335679202476</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>5.931467449995171</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>5.2779</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0.3130569205432951</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>0.8376159843869582</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>-1.5677528</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>7.2872</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>6.68326</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.6039400000000006</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0.410160635688245</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>6.137134208279268</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>5.3401</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0.3277291038563211</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>0.8768729196673477</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>-0.7188652499999998</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>7.176125</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0.5161249999999997</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0.1880718872989345</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>2.823902211695714</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>5.2312</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0.1477239724982262</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>0.3952506797387386</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>-0.9294246000000002</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>7.06265</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>6.621775</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0.4408750000000001</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0.2431591158761081</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>3.67211383467587</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>5.2153</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0.1915117528198506</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>0.5124093889426929</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>-0.9052640000000001</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>6.952679999999999</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>6.57676</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0.3759199999999989</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0.2368381403660599</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>3.601137039607039</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>5.1423</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>0.1851812699877128</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>0.4813152016640412</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>-1.17526025</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>6.787225</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>6.5576</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.2296250000000004</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0.1891321427640174</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0.3074754458988214</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>4.688841129358628</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>5.1285</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>0.2404672173191572</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>0.6250120609132914</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/planilhas/ipca-defasagem.xlsx
+++ b/planilhas/ipca-defasagem.xlsx
@@ -11,7 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modelo mensal" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por ponto" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contrafactual Bahia" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidade" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contrafactual Salvador" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Praças e pesos" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IPCA 12 meses" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidade" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A57"/>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -696,98 +699,178 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Contrafactual Bahia | A segunda estimativa, por grupo de controle</t>
+          <t>Contrafactual Bahia | Segunda estimativa: preço de bomba baiano como controle</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sensibilidade | O mesmo cálculo com a margem escalando junto</t>
+          <t>Contrafactual Salvador | Terceira estimativa: o método da FGV, estendido para série mensal</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Praças e pesos | Os pesos regionais recuperados e a réplica da tabela T.2 do artigo</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>DUAS ESTIMATIVAS, E ELAS NÃO BATEM</t>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>IPCA 12 meses | O acumulado observado e como ficaria em cada estimativa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A contábil supõe que R$ 1,00 na refinaria vira R$ 0,70 na bomba, porque 70% do litro é gasolina A.</t>
+          <t>Sensibilidade | O mesmo cálculo com a margem escalando junto</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A da Bahia MEDE quanto aparece, usando a Acelen (que segue o PPI) como controle, e acha R$ 0,26.</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A contábil é teto e a da Bahia é piso. O teto supõe repasse integral e imediato; o piso subestima</t>
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>TRÊS ESTIMATIVAS, E ELAS NÃO BATEM</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>porque a Acelen não atende a Bahia inteira, não segue o PPI perfeitamente e também recebeu as</t>
+          <t>1. CONTÁBIL. Supõe que R$ 1,00 na refinaria vira R$ 0,70 na bomba, porque 70% do litro é gasolina A.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>subvenções de 2026, que encolhem o próprio spread que serve de medida. A verdade mora no meio,</t>
+          <t xml:space="preserve">   Nada é estimado. Supõe repasse integral e imediato, e por isso é TETO.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>e a largura entre as duas é a sua incerteza honesta.</t>
+          <t>2. BAHIA. MEDE quanto do repasse aparece, usando o preço de bomba baiano (Acelen, que segue o PPI)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   como controle. Acha R$ 0,26 por real de defasagem, não R$ 0,70. É PISO: a Acelen não atende a</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>ATENÇÃO — a tabela mais recente da Petrobras é de 01/09/2026.</t>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Bahia inteira, não segue o PPI perfeitamente e também recebeu as subvenções de 2026, que encolhem</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Depois dessa data o preço segue valendo até mudar. Reajuste que ainda não apareceu não está aqui.</t>
+          <t xml:space="preserve">   o próprio spread que serve de medida.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3. SALVADOR (FGV). Compara a VARIAÇÃO do IPCA Gasolina de cada praça com a de Salvador e imputa a</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Fontes: PPI e preços de revenda da ANP; tabela de preços da Petrobras; IPCA da tabela 7060 do</t>
+          <t xml:space="preserve">   diferença à defasagem. Não é ideia nossa: é o método de Francisco Pessoa Faria no Blog do IBRE,</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   'Impacto da defasagem da gasolina no IPCA e reflexos de sua subvenção nos resultados da Petrobras'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ele roda a conta uma vez, no bimestre mar-abr/2026, e acha 0,59 p.p.; aqui ela roda todo mês. A aba</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   'Praças e pesos' reproduz a tabela T.2 dele para mostrar que é a mesma conta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>A 2 e a 3 usam a mesma intuição (a Bahia como mercado sem defasagem) por caminhos diferentes: a 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>compara NÍVEL de preço em R$/l e por isso desconta um spread estrutural; a 3 compara VARIAÇÃO, onde</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>diferença permanente de nível some sozinha. A largura entre as três é a sua incerteza honesta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>ATENÇÃO — a tabela mais recente da Petrobras é de 01/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Depois dessa data o preço segue valendo até mudar. Reajuste que ainda não apareceu não está aqui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Fontes: PPI e preços de revenda da ANP; tabela de preços da Petrobras; IPCA da tabela 7060 do</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>SIDRA (IBGE); teor de anidro pela legislação (CNPE e MAPA).</t>
         </is>
@@ -7494,13 +7577,13 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10467,6 +10550,4041 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F91"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Terceira estimativa: Salvador como contrafactual (o método da FGV, estendido)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>O IPCA mede a gasolina em 16 praças. Em Salvador a Petrobras não tem ponto de entrega e quem forma</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>preço é a Acelen, que segue o PPI. Então a variação do subitem Gasolina em Salvador é uma leitura de</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mercado do que a gasolina teria feito no país sem defasagem. A diferença entre o que cada praça fez e</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>o que Salvador fez, ponderada pelo peso da praça no índice nacional, é o represamento do mês.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Não é conta nossa. É a de Francisco Pessoa Faria, no Blog do IBRE da FGV. Ele roda uma vez, no</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bimestre março-abril de 2026, e acha 0,59 p.p.; aqui ela roda todo mês. A aba 'Praças e pesos' mostra</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>a réplica da tabela T.2 dele, número a número, que é a prova de que é o mesmo método.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Começa em 2022-01 porque a Acelen comprou a RLAM em 30/11/2021. Antes disso a refinaria era da</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Petrobras e Salvador não servia de contrafactual de nada. E a janela só fica limpa de verdade a partir</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>de 2023-06, quando o ICMS virou monofásico: antes, mudança de alíquota num estado entrava na conta</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>como se fosse defasagem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ATENÇÃO AO SINAL. Em mês de defasagem crescente Salvador sobe mais que o resto e o impacto é</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>positivo. Quando a defasagem encolhe, ou quando algo local mexe no preço baiano, Salvador sobe menos</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>e o impacto fica NEGATIVO. Isso não é erro: é o preço de estender para série mensal uma conta que o</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>artigo faz num bimestre escolhido justamente por ser o do choque. A coluna 'praças acima de Salvador'</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>é o termômetro: quando ela é alta, o contrafactual daquele mês não está medindo defasagem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>O QUE ESTA ESTIMATIVA NÃO VÊ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ela mede só a parte do represamento que NÃO é comum a Salvador. No bimestre do choque isso era quase</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>tudo: Salvador repassou na hora e o resto do país não. Depois duas coisas estreitaram a diferença.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Primeiro, as outras praças correram atrás, e correr atrás some do acumulado em doze meses. Segundo, a</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>subvenção da MP 1.358 vale para TODO produtor e importador desde junho de 2026, Acelen inclusive: o</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>preço baiano também passou a ser segurado, e o controle deixou de ser controle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>É por isso que o acumulado em 12 meses por este caminho vai a zero em setembro de 2026 enquanto o</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>contábil ainda marca 0,8 p.p. Os dois podem estar certos ao mesmo tempo: o contábil mede o nível da</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>defasagem no portão da refinaria, este mede o quanto uma praça andou diferente da outra. Quando as duas</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>estão seguradas pelo mesmo programa, a diferença some e a defasagem fica onde estava.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>mês</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>var. Salvador %</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>praças acima de Salvador</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>impacto do mês (p.p.)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>IPCA mês %</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>IPCA mês contrafactual %</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0.07035784214690771</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.6103578421469078</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0.07495976781537249</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1.084959767815372</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="C37" t="n">
+        <v>7</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>-0.01031607087721543</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1.609683929122785</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="C38" t="n">
+        <v>15</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>-0.4156336767950466</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0.6443663232049535</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0.3889659680066927</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0.8589659680066927</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0.3702631951740569</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1.040263195174057</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>-16.97</v>
+      </c>
+      <c r="C41" t="n">
+        <v>9</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>-0.1094658730916288</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>-0.7894658730916289</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="C42" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>-0.03294240059681942</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>-0.3929424005968194</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>-7.18</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0.06540266696580335</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>-0.2245973330341966</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0.0989625227344611</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0.6889625227344611</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0.018047288181886</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0.428047288181886</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>-7.15</v>
+      </c>
+      <c r="C46" t="n">
+        <v>15</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>-0.2884680138042853</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.3315319861957147</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0.2573702171384694</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.7873702171384694</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C48" t="n">
+        <v>14</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>-0.0890497073151976</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0.7509502926848024</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="C49" t="n">
+        <v>9</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>-0.01368802829460854</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0.6963119717053914</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>-0.03122633617868503</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0.578773663821315</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>-8.609999999999999</v>
+      </c>
+      <c r="C51" t="n">
+        <v>15</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>-0.3347799858759103</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>-0.1047799858759103</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="C52" t="n">
+        <v>7</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0.01216280183053876</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>-0.06783719816946124</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0.2894984855630253</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0.4094984855630253</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0.06625605451240257</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0.2962560545124026</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C55" t="n">
+        <v>13</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>-0.09897341458003038</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>0.1610265854199696</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>9</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0.02112403006288471</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0.2611240300628847</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="C57" t="n">
+        <v>12</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>-0.09811635484224135</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0.1818836451577587</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C58" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>-0.01073828620756138</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0.5492617137924387</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="C59" t="n">
+        <v>9</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>-0.02956669361462199</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0.390433306385378</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0.04670216161881782</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0.8767021616188178</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="C61" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0.02524114212486263</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0.1852411421248626</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0.04445635687386914</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0.4244563568738691</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0.09156682861988309</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>0.5515668286198832</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="C64" t="n">
+        <v>12</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>-0.04779053564224642</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0.1622094643577536</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="C65" t="n">
+        <v>15</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>-0.1786708224324393</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0.2013291775675607</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0.2097822766677853</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0.1897822766677853</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="C67" t="n">
+        <v>12</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>-0.114156551351909</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0.3258434486480911</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="C68" t="n">
+        <v>11</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>-0.0323750054094743</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0.5276249945905258</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="C69" t="n">
+        <v>14</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>-0.1051988074774702</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0.2848011925225298</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0.1823881362964981</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0.7023881362964981</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="C71" t="n">
+        <v>15</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>-0.07106086435991452</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0.08893913564008549</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="C72" t="n">
+        <v>13</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>-0.1091967748496407</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1.200803225150359</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="C73" t="n">
+        <v>11</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>-0.02727272599091173</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0.5327272740090884</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="C74" t="n">
+        <v>14</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>-0.09774957019957448</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0.3322504298004255</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C75" t="n">
+        <v>5</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0.04584689293590623</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.3058468929359062</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0.1568290877241253</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>0.3968290877241253</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="C77" t="n">
+        <v>15</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>-0.1728981647982739</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0.0871018352017261</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0.1138332624844519</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0.003833262484451858</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="C79" t="n">
+        <v>10</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>-0.05071199984184536</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0.4292880001581546</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C80" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.05595049424009547</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.1459504942400955</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="C81" t="n">
+        <v>14</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>-0.09993051483792986</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0.08006948516207013</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C82" t="n">
+        <v>14</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>-0.05908088512306089</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0.2709191148769391</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0.06429960621375989</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0.3942996062137599</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="C84" t="n">
+        <v>15</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>-0.1524773349539384</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0.5475226650460615</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0.6290779171934394</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>1.509077917193439</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C86" t="n">
+        <v>12</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>-0.05920827207165286</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0.6107917279283471</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="C87" t="n">
+        <v>14</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>-0.1057555537760053</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0.4742444462239946</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0.109827564003661</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.269827564003661</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="C89" t="n">
+        <v>14</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>-0.1077737113809358</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>-0.03777371138093584</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="C90" t="n">
+        <v>15</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>-0.1930562569446283</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>-0.5130562569446283</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="C91" t="n">
+        <v>13</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>-0.07940519098689489</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0.740594809013105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Os pesos regionais, e a réplica da tabela T.2 do artigo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>O SIDRA publica o peso de cada subitem DENTRO de cada praça, e esses sempre somam 100. O peso da</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>praça no índice nacional ele não publica. Mas o peso nacional de cada subitem é a média dos pesos</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>locais ponderada pelas praças, e essa identidade vale para os 210 níveis de agregação de uma vez:</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>210 equações para 16 incógnitas, resolvidas por mínimos quadrados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A verificação: os pesos somam 100.0000 (tem que dar 100) e o pior resíduo das 210 equações é 0.000064,</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>que é o arredondamento do próprio SIDRA. Se isso parasse de fechar, o script aborta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>praça</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>peso no IPCA nacional %</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>peso da gasolina na praça %</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>contribuição da gasolina (p.p.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>32.27997098669594</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>4.056</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1.309275623220387</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>9.690815499370069</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>5.1074</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.494948710814827</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>9.429956398037689</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>3.6602</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0.3451552640809755</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>8.607464899193953</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>6.3182</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0.5438368472608723</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>8.091192764675643</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>6.809</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0.5509293153467646</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>5.990856986967537</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>4.7098</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.2821573823721971</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>4.169018801910871</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>6.6286</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.276347580303464</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>4.060531243424002</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>7.1724</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0.2912375429033431</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>3.939786395180093</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>5.7116</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0.2250248397471062</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Recife</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>3.9202041293611</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>6.082</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.2384268151477421</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>3.229588389922799</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>5.5426</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.1790031660998611</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Grande Vitória</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1.859817504228769</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>5.0721</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.0943318036319874</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>São Luís</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>1.620579278961622</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>5.8396</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.0946353475742429</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1.570347017649928</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>7.3312</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.1151252805579515</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Aracaju</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1.029935678854167</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>5.6568</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0.0582614014814225</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0.5099387828922411</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>5.8424</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0.02979266345169629</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>(peso da gasolina: 2026-09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Réplica da T.2: bimestre 2026-03 a 2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>As colunas 'FGV' são as publicadas no artigo. Se batem, o método aqui é o dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>praça</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>var. observada %</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>FGV</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>var. imputada %</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>FGV</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>impacto (p.p.)</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>FGV</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Aracaju</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>10.72759999999999</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>6.740857744591233</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.003936829624227072</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>2.887046999999998</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>14.87509209978588</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.07646530802771984</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Belém</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>9.286135999999988</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>8.148749993320292</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.01851553275625435</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Brasília</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>0.9790909999999986</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>17.04560699600673</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0.04954423065385865</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.049</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>7.821831000000001</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>9.617494809562267</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.01118272040956847</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Curitiba</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>5.709169999999997</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>11.80826601892722</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0.06743230789200401</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>7.616960000000006</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>9.826174238707353</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0.01767992365873773</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0.019</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Goiânia</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>2.565169000000012</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>15.23560205901866</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0.04031138863697042</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Grande Vitória</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>6.914759999999998</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>10.54749596781586</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0.01012383697297717</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.011</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Porto Alegre</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>5.290360000000005</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>12.25300207920268</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0.07233790164601371</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Recife</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>10.55048299999999</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>6.911871203674447</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0.01748718165158855</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Rio Branco</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>4.292804000000006</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>13.32669701737044</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0.004005172485856322</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>7.471880000000009</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>9.974432381754173</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0.03419683519480692</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>18.19158999999999</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>São Luís</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>13.18670000000002</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>4.421800441217894</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.004042773487586994</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>6.279199999999996</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>11.20858079473688</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0.150495977115013</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0.5777579202131832</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>O IPCA acumulado em 12 meses, e como ficaria em cada estimativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cada contrafactual é o IPCA mensal observado mais o que o item Gasolina teria feito a mais naquele</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mês, acumulado em doze meses. Só entram janelas de doze meses seguidos e completos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>O contábil e o da Bahia dependem do preço de bomba da ANP e da tabela da Petrobras; o de Salvador</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>depende só do IPCA regional do IBGE. São três fontes e três hipóteses diferentes para o mesmo número,</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>e é por isso que a distância entre eles é informação, não ruído.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LEMBRE DO QUE É CADA UM: contábil é TETO (repasse integral e imediato), Bahia é PISO (mede o repasse</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>que de fato apareceu no preço baiano), Salvador fica no meio e o próprio autor o chama de limite</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>superior da ordem de magnitude.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>E leia a coluna de Salvador junto com a aba dela. Ela não mede nível de defasagem, mede diferença de</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ritmo entre praças, então ela zera quando todo mundo repassa igual — inclusive quando todo mundo está</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>igualmente segurado, que é o caso desde a subvenção de junho de 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>mês</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>IPCA 12m observado %</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>contrafactual contábil %</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>contrafactual Bahia %</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>contrafactual Salvador %</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>efeito contábil (p.p.)</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>efeito Bahia (p.p.)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>efeito Salvador (p.p.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>10.0610548932579</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>9.962603986575713</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-0.09845090668219036</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>10.3794359996823</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>10.21386521640943</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>10.31512380193014</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-0.1655707832728623</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-0.0643121977521588</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>10.54359340003879</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>10.57589295646273</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>10.55214872624888</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.03229955642394167</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.008555326210089476</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>11.299315974556</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>11.51932196508123</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>11.37673778021888</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.2200059905252285</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0.07742180566287971</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>12.13148113237592</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>11.96466834664522</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>12.06557252565577</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>-0.1668127857306967</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-0.0659086067201553</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>11.73113070881493</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>12.19372120333835</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>11.89082896398763</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0.4625904945234183</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0.1596982551727013</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>11.88672961759074</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>12.43538597593616</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>12.07819889371859</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0.548656358345422</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0.1914692761278527</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>10.06923519828753</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>10.04766638536494</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>10.04913752233285</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-0.02156881292258994</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-0.02009767595467693</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>8.727060525006136</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>8.712041513891711</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>8.709810509190685</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>-0.0150190111144255</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-0.01725001581545094</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>7.168596332032062</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>7.032565002380919</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>7.108413315422424</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-0.1360313296511428</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-0.06018301660963843</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>6.470015852238076</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>6.353013205261271</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>6.413873111236601</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>-0.1170026469768048</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>-0.05614274100147476</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>5.900488278585692</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>5.967643734186945</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>5.912552222439715</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0.06715545560125324</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0.01206394385402376</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>5.784841959607756</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>5.726304292427931</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>5.751181212649903</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>6.025054123071283</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>-0.05853766717982545</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>-0.03366074695785315</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0.2402121634635268</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>5.774320292414625</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>5.803957290504713</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>5.770727097885642</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>6.211593034585516</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0.02963699809008791</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-0.003593194528983545</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0.4372727421708911</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>5.596301933344128</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>5.310573375490191</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>5.477991256373249</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>5.860643907002649</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>-0.285728557853937</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>-0.1183106769708786</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.2643419736585217</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>4.65069442734789</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>4.361390806598586</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>4.529973669120624</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>4.909059965394857</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>-0.2893036207493038</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>-0.1207207582272662</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0.2583655380469674</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>4.184705782064824</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>4.303154778105966</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>4.214727203542146</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>4.840687889659612</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.1184489960411428</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.03002142147732201</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0.655982107594788</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>3.935832194051536</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>3.385956707192284</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>3.726354581810298</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>3.838895061563652</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>-0.5498754868592526</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>-0.2094776122412378</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>-0.09693713248788427</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>3.161501468457617</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>2.767076158402193</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>3.005444492143727</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>2.700102298921947</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>-0.394425310055424</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>-0.1560569763138897</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>-0.4613991695356701</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>3.992443888662711</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>4.125262686135378</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>4.032574781794529</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>3.941238266692126</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.1328187974726669</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0.04013089313181784</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>-0.05120562197058476</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>4.608216087521688</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>4.901091124729029</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>4.706290942967595</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>4.66042566728424</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0.2928750372073408</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0.09807485544590655</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0.05220957976255214</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>5.185234629775626</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>5.482154230507463</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>5.283125806607969</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>5.064929807323781</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0.2969196007318375</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0.09789117683234316</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>-0.1203048224518444</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>4.819245643589931</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>4.740897257313037</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>4.784546213145879</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>4.618497347646122</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>-0.07834838627689411</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>-0.03469943044405177</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>-0.2007482959438089</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>4.683537029570672</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>4.569723251380831</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>4.636160692660374</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>4.362062306537484</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>-0.1138137781898418</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>-0.04737633691029863</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>-0.3214747230331882</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>4.621113930566789</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>4.734190422349682</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>4.656249341249352</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>4.58853869883018</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0.113076491782893</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0.03513541068256298</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>-0.03257523173660903</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>4.506637430692439</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>4.40718508205209</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>4.466906349310973</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>4.176631419556509</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>-0.0994523486403498</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>-0.03973108138146664</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>-0.3300060111359304</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>4.496273821268559</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>4.750326192333731</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>4.584253568359253</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>4.306659037779448</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0.2540523710651721</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0.087979747090694</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>-0.1896147834891115</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>3.925596126881703</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>4.194660779031967</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>4.019955746040726</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>3.777264368586497</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0.2690646521502638</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0.09435961915902347</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>-0.148331758295206</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>3.688016491565316</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>4.054052861338309</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>3.818240323625877</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>3.618039639785797</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.3660363697729929</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0.1302238320605609</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>-0.06997685177951851</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>3.92595167856582</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>4.245711711167188</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>4.036601874972368</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>4.29884669173739</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.3197600326013683</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0.1106501964065476</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0.3728950131715703</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>4.227578239682583</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>4.417010450114822</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>4.293740786088862</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>4.538945583967391</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0.1894322104322388</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.06616254640627872</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.3113673442848075</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>4.498245142821999</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>4.607380637949898</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>4.535906645719212</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>4.322215092440063</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0.1091354951278989</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.03766150289721271</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>-0.1760300503819368</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>4.237599016056492</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>4.079085282302719</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>4.176629053218628</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>4.211467385686496</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>-0.1585137337537734</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>-0.0609699628378646</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>-0.02613163036999655</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>4.424740127395888</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>4.242420348778775</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>4.356027294426768</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>4.382949325842778</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>-0.1823197786171127</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>-0.06871283296912001</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>-0.04179080155310988</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>4.758099233947855</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>4.755848061625612</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>4.754076868365709</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>4.660406385542548</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>-0.002251172322242923</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>-0.004022365582145859</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>-0.09769284840530634</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>4.87301138907088</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>4.966153213212099</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>4.903273396267971</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>4.767924750535069</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0.09314182414121852</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0.03026200719709049</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>-0.1050866385358118</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>4.831295791859591</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>5.007783595970206</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>4.891642864161216</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>4.927475772957202</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0.1764878041106144</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0.06034707230162528</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>0.0961799810976105</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>4.559874392677332</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>4.742327782715416</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>4.622586202201662</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>4.612355882997021</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>0.1824533900380843</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0.06271180952432953</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>0.05248149031968907</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>5.057630414778758</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>5.043635090131948</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>5.049444854567375</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>4.948459017553208</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>-0.01399532464680942</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>-0.008185560211382281</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>-0.1091713972255492</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>5.477189641674851</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>5.307725236457728</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>5.41243851851072</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>5.312466067448773</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>-0.1694644052171235</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>-0.06475112316413068</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>-0.1647235742260778</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>5.52972858849774</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>5.141826518258452</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>5.385189909867272</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>5.215772155244425</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>-0.3879020702392877</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>-0.1445386786304681</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>-0.3139564332533151</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>5.319635559255276</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>5.069974228174234</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>5.227670658008488</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>4.958654204899715</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>-0.2496613310810414</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>-0.09196490124678824</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>-0.3609813543555607</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>5.35116523759851</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>5.113737996126</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>5.262698388554976</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>5.204509004332425</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>-0.2374272414725098</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>-0.08846684904353364</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>-0.1466562332660848</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>5.225222422012621</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>4.876716262120961</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>5.096460485912813</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>5.084578145459595</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>-0.3485061598916595</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>-0.1287619360998082</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>-0.1406442765530258</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>5.130500777503921</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>4.962119683481525</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>5.067305632341257</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>4.889544547541758</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>-0.1683810940223962</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>-0.06319514516266445</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>-0.2409562299621637</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>5.172368758697643</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>5.139626366935546</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>5.15813050286793</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>4.997694666402852</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>-0.03274239176209726</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>-0.01423825582971272</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>-0.1746740922947909</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>4.680811347037062</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>4.517360563655481</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>4.619606772071294</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>4.599048596211675</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>-0.1634507833815801</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>-0.06120457496576748</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>-0.08176275082538709</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>4.461835648432833</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>4.318961684332367</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>4.408581573859238</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>4.385509340484695</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>-0.142873964100465</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>-0.05325407457359432</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>-0.07632630794813799</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>4.264384904568952</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>3.949720399175249</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>4.148091078783556</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>3.93825963370944</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>-0.3146645053937025</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>-0.1162938257853963</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>-0.3261252708595119</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>4.44135121281346</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>4.093500553761986</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>4.312921746389908</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>4.255363962583902</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>-0.3478506590514741</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>-0.1284294664235519</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>-0.1859872502295579</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>3.812496961112588</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>3.702103518412247</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>3.771184983109976</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>3.582365326280246</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>-0.1103934427003406</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>-0.04131197800261166</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>-0.2301316348323423</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>4.142846991219562</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>4.705260846416071</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>4.35235009218129</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>4.588333350337015</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0.5624138551965085</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0.2095031009617276</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>0.4454863591174529</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>4.39171967147336</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>5.295527146947721</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>4.733003334691599</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>4.87869033939734</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0.9038074754743608</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0.3412836632182392</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>0.4869706679239805</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>4.724906887660008</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>5.714195495078256</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>5.097921684388296</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>5.05476496906534</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0.9892886074182483</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0.3730147967282882</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>0.329858081405332</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>4.641327552554153</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>5.118594110411356</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>4.810730405229013</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>4.921871178032311</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0.4772665578572033</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0.1694028526748603</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>0.2805436254781579</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>4.44302461783459</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>5.099231024975936</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>4.680045402030419</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>4.790963440955354</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0.6562064071413465</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0.2370207841958294</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>0.3479388231207636</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>4.223452737068278</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>4.864088098430419</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>4.460606433499792</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>4.249330695825138</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0.6406353613621407</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0.2371536964315135</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>0.02587795875685917</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>4.576119675071877</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>5.376001837431188</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>4.876932596839412</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>4.572478724755991</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.7998821623593111</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0.3008129217675348</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>-0.003640950315886293</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/planilhas/ipca-defasagem.xlsx
+++ b/planilhas/ipca-defasagem.xlsx
@@ -692,7 +692,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Por ponto | O nível represado em cada ponto de entrega</t>
+          <t>Por ponto | O nível represado em cada ponto de entrega, com a média ponderada por produção</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4920,2643 +4920,3221 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>mês</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Araucária (PR)</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Betim (MG)</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Canoas (RS)</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Cubatão (SP)</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Duque de Caxias (RJ)</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Guamaré (RN)</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Manaus (AM)</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Paulínia (SP)</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>São José dos Campos (SP)</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>O nível represado em cada ponto de entrega da Petrobras</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020-01</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>-0.02205382038992319</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>-0.041128783638849</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>-0.03840311304127079</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.004919029538471642</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>-0.02024138321377418</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0.04540538495052733</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>-0.00936349744369229</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>-0.04050136389272234</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>-0.006063426189298285</v>
+          <t>Mesma conta do Modelo mensal, repetida nos nove pontos em que a tabela da Petrobras e o PPI da ANP</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020-02</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0.04920962223973733</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.0378409402529143</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.02592071854737574</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.08436641626350465</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.04168585404845777</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0.1425251155380308</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0.08305442338760594</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>0.03847550967153363</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0.07181924821353143</v>
+          <t>existem no mesmo lugar. O Modelo mensal é Paulínia, e só.</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2020-03</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>-0.3140749261466558</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>-0.3249675162194146</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>-0.3360903655911032</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>-0.2782091413903178</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>-0.3211048750663227</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>-0.2272671704500882</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>-0.2870364380750129</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>-0.3243314041993494</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>-0.2908195652255967</v>
-      </c>
+      <c r="A4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020-04</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>-0.1754876039303373</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>-0.1868113088168932</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>-0.1982179865658275</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>-0.1371110044265618</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>-0.1827038219984097</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>-0.0866894743863257</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>-0.1502174153748289</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>-0.1861334403391066</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>-0.1505145330517807</v>
+          <t>QUAL MÉDIA USAR. Se a empresa fechar a defasagem, cada ponto sobe o tanto do dele e o preço nacional</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2020-05</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0.2258227077428413</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0.2881676652171895</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.2046747110026426</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.2515616467144952</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0.2808934443886905</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0.3560969812791875</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0.2124780509309</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0.2327088618026509</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0.2585625786515474</v>
+          <t>sobe a média PONDERADA PELO VOLUME, não a simples. A simples dá a Manaus o mesmo peso de Paulínia, e</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2020-06</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0.1355733672727274</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0.1961305068870524</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.1147212782369147</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.1588788574104684</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0.1888305767493114</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0.2734981971349863</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0.135918421046832</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0.1420565757575759</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0.1656306657851241</v>
+          <t>os dois não se parecem: a REAM é da Atem desde 2022 e não tem produção da Petrobras atrás, enquanto</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2020-07</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>0.07629908940855064</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0.1392595589551427</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0.05618541191214688</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.09901315176443581</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0.1316141841124636</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0.2100906675666332</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0.07082086205127598</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>0.08358439372118619</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0.1066332304115849</v>
+          <t>Paulínia sozinha é um quarto da gasolina A da empresa. Por isso a simples sai sempre mais baixa.</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2021-01</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>0.2730367586215735</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0.3367636651083001</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>0.2523015234793388</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0.2948576880830346</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0.328966171637224</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0.4135613242006753</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>0.2461911478375368</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>0.2804601960071318</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>0.3031434169216938</v>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2021-02</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>0.189117096608565</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>0.2444647800394101</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0.1692372825386691</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0.2022565645959802</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0.2369344766143923</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0.3230544107788523</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0.1638794085486674</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>0.1904546953845448</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.2117343699570627</v>
+          <t>O peso é a produção de gasolina A, em janela de doze meses, da refinaria atrás de cada ponto:</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2021-03</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>0.1157693573804219</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>0.1765731677494634</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0.1095717561282882</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0.1317270165773615</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0.1688276767540805</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0.2572848661573447</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0.1016101647967639</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>0.1222065172288699</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>0.1420479401972188</v>
+          <t xml:space="preserve">   REDUC = Duque de Caxias, REFAP = Canoas, REGAP = Betim, REPAR = Araucária, REPLAN = Paulínia, REVAP = São José dos Campos, RPBC = Cubatão.</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2021-04</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>0.09835569198631301</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>0.1672208041479903</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0.09612952562444603</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0.1187095046505268</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0.1588037407429615</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>0.250168899744053</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>0.08608523762562034</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>0.1078278916628841</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>0.1298293438212224</v>
+          <t>Manaus e Guamaré entram nas colunas e na média simples, mas não na ponderada: a Petrobras entrega</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2021-05</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>0.04193254462900337</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>0.1028628123130621</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0.03999532709301898</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0.06278074983924074</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0.09554838326151505</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>0.1754503915958079</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>0.03091218404264126</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>0.04962868577491895</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0.07162088098569633</v>
+          <t>ali e não refina, então não há volume dela para pesar.</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2021-06</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>0.02284419488292146</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>0.07866046521103269</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>0.02003067161337154</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0.04472033275180928</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.07211011182409528</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0.1570034719781113</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>0.0180482774988968</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0.02933564634170345</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0.05185530689969101</v>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2021-07</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>0.1413764030044583</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>0.1981797976383159</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>0.1388040519305375</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0.162475300331321</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.1914501919204304</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0.2732445864112646</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>0.1345979732429458</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>0.1482219846044359</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0.1701411258642319</v>
+          <t>É aproximação, porque a empresa também entrega de terminal e não só da refinaria do lado. Erra pouco</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2021-08</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>0.06010313801351393</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>0.118319476392254</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>0.05758765142134232</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0.08046491230233499</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0.1113603328685366</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>0.1923508747480611</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>0.05345131972396523</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.06742981592184363</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.08876343238746437</v>
+          <t>e erra parelho; o que ela conserta é o peso dos dois pontos sem refinaria dela atrás, que é onde</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2021-09</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>0.04761243639303924</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>0.1053480001790478</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>0.04488628790402167</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>0.06792176590861326</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0.09845891953408044</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0.181942724769328</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>0.0441900822399916</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>0.05492433775469161</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>0.07611744691225274</v>
+          <t>a média simples se perde.</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2021-10</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>0.3029002430473683</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>0.3643093715366567</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0.3006395842446443</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0.3216744107606022</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>0.3568253378389514</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>0.4325285129517925</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>0.2925089941189263</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>0.3112039157566914</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>0.3313687519639826</v>
-      </c>
+      <c r="A18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2021-11</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>0.1238809413067367</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>0.1827686908880636</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>0.1223495275810151</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>0.1414356373989095</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>0.1755559632428736</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0.2404924233595447</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>0.1067075699499504</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>0.1317875271007257</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>0.1508761847453593</v>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>mês</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Araucária (PR)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Betim (MG)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Canoas (RS)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Cubatão (SP)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Duque de Caxias (RJ)</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Guamaré (RN)</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Manaus (AM)</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Paulínia (SP)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>São José dos Campos (SP)</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>média ponderada por produção</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>média simples</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2020-01</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.02473520904490717</v>
+        <v>-0.02205382038992319</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.08984530307160851</v>
+        <v>-0.041128783638849</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.0230281679395012</v>
+        <v>-0.03840311304127079</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.04317200998599571</v>
+        <v>0.004919029538471642</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.0818202009074783</v>
+        <v>-0.02024138321377418</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.1506480516926524</v>
+        <v>0.04540538495052733</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.005104818642516982</v>
+        <v>-0.00936349744369229</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.03369419051068995</v>
+        <v>-0.04050136389272234</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.05394983603398375</v>
+        <v>-0.006063426189298285</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>-0.0252631806860144</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>-0.01415899703561457</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2020-02</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.1703938507836436</v>
+        <v>0.04920962223973733</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.2329024039859901</v>
+        <v>0.0378409402529143</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.1683238704152898</v>
+        <v>0.02592071854737574</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.1892853874274027</v>
+        <v>0.08436641626350465</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.2252681628007171</v>
+        <v>0.04168585404845777</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.297592867547735</v>
+        <v>0.1425251155380308</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.1553631743649436</v>
+        <v>0.08305442338760594</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1788333358850688</v>
+        <v>0.03847550967153363</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.1992250604185014</v>
+        <v>0.07181924821353143</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0.04892584764334269</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0.06387753868474351</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2020-03</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.2553201171580137</v>
+        <v>-0.3140749261466558</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.3103310677944811</v>
+        <v>-0.3249675162194146</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.2533962959398685</v>
+        <v>-0.3360903655911032</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.2751089377732542</v>
+        <v>-0.2782091413903178</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.3037704404445927</v>
+        <v>-0.3211048750663227</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.3742084415409008</v>
+        <v>-0.2272671704500882</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.241044533961943</v>
+        <v>-0.2870364380750129</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.2619730192567931</v>
+        <v>-0.3243314041993494</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.2827459250331652</v>
+        <v>-0.2908195652255967</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>-0.3137000842281468</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>-0.3004334891515402</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.3365408384714535</v>
+        <v>-0.1754876039303373</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.3849893706144007</v>
+        <v>-0.1868113088168932</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.3353841708418631</v>
+        <v>-0.1982179865658275</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.3555352111709251</v>
+        <v>-0.1371110044265618</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.3792773361993583</v>
+        <v>-0.1827038219984097</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.4382152528622338</v>
+        <v>-0.0866894743863257</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.3163874437738521</v>
+        <v>-0.1502174153748289</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.3418654110925772</v>
+        <v>-0.1861334403391066</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.3616999570222661</v>
+        <v>-0.1505145330517807</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>-0.1746553532268532</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>-0.161542954321119</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2020-05</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-0.02312229045965181</v>
+        <v>0.2258227077428413</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.02022681987330523</v>
+        <v>0.2881676652171895</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-0.021909236967736</v>
+        <v>0.2046747110026426</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-0.003334880577496748</v>
+        <v>0.2515616467144952</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.01523405434462271</v>
+        <v>0.2808934443886905</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.0615657853639599</v>
+        <v>0.3560969812791875</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-0.05550593937250058</v>
+        <v>0.2124780509309</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>-0.01930015543484413</v>
+        <v>0.2327088618026509</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.001180795756600123</v>
+        <v>0.2585625786515474</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.2458657231527421</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0.2567740719700161</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0.4780317896439253</v>
+        <v>0.1355733672727274</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.5264630693295475</v>
+        <v>0.1961305068870524</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.4806454957981513</v>
+        <v>0.1147212782369147</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.4978425097382929</v>
+        <v>0.1588788574104684</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5208262854651194</v>
+        <v>0.1888305767493114</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.6057700311828927</v>
+        <v>0.2734981971349863</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.4881706380473486</v>
+        <v>0.135918421046832</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.483548250311634</v>
+        <v>0.1420565757575759</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.5037485721449538</v>
+        <v>0.1656306657851241</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0.154420934314285</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0.1679153829201103</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.5390506961180702</v>
+        <v>0.07629908940855064</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.5880556475204872</v>
+        <v>0.1392595589551427</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.5421732255625863</v>
+        <v>0.05618541191214688</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.5588877101984873</v>
+        <v>0.09901315176443581</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.5823408618073536</v>
+        <v>0.1316141841124636</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.667160583442609</v>
+        <v>0.2100906675666332</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.548865290175667</v>
+        <v>0.07082086205127598</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.5446601125248454</v>
+        <v>0.08358439372118619</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.5649357370512414</v>
+        <v>0.1066332304115849</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0.09582934691287802</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0.1081667277670467</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.04525216794032216</v>
+        <v>0.2730367586215735</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.1090009724800244</v>
+        <v>0.3367636651083001</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.05116126015741487</v>
+        <v>0.2523015234793388</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.06653983224949382</v>
+        <v>0.2948576880830346</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.1013291754521733</v>
+        <v>0.328966171637224</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.1947213168383227</v>
+        <v>0.4135613242006753</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.05172106559161968</v>
+        <v>0.2461911478375368</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.05351796417784904</v>
+        <v>0.2804601960071318</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.07598013761880193</v>
+        <v>0.3031434169216938</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.2929382481717085</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0.3032535435440565</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-0.04798700003292294</v>
+        <v>0.189117096608565</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.0102494568946281</v>
+        <v>0.2444647800394101</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-0.04311766436815226</v>
+        <v>0.1692372825386691</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-0.02639672309183706</v>
+        <v>0.2022565645959802</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.003354235238600175</v>
+        <v>0.2369344766143923</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.09641461013663047</v>
+        <v>0.3230544107788523</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>-0.03956555724397762</v>
+        <v>0.1638794085486674</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>-0.04088201883928078</v>
+        <v>0.1904546953845448</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>-0.01851789409763527</v>
+        <v>0.2117343699570627</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0.2037542790750742</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0.2145703427851271</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2021-03</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.1782963026246124</v>
+        <v>0.1157693573804219</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.1214738193324258</v>
+        <v>0.1765731677494634</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.1719764432360556</v>
+        <v>0.1095717561282882</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.1579850883659235</v>
+        <v>0.1317270165773615</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.1282407662190511</v>
+        <v>0.1688276767540805</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.0413783862673805</v>
+        <v>0.2572848661573447</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.1721716422221407</v>
+        <v>0.1016101647967639</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.1712064592116029</v>
+        <v>0.1222065172288699</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.1500349667866955</v>
+        <v>0.1420479401972188</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0.1346954509080347</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0.1472909403299792</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>0.1181894702195957</v>
+        <v>0.09835569198631301</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.173757033273074</v>
+        <v>0.1672208041479903</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.1220245882026819</v>
+        <v>0.09612952562444603</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.137734595247146</v>
+        <v>0.1187095046505268</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.1671251662656948</v>
+        <v>0.1588037407429615</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.2530602565844705</v>
+        <v>0.250168899744053</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.125493347593237</v>
+        <v>0.08608523762562034</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1252251081613263</v>
+        <v>0.1078278916628841</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.1456222463318141</v>
+        <v>0.1298293438212224</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0.1214486599939314</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>0.1347922933340019</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0.1019018402948163</v>
+        <v>0.04193254462900337</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.154806374266328</v>
+        <v>0.1028628123130621</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.1073188646786817</v>
+        <v>0.03999532709301898</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.1203095988575679</v>
+        <v>0.06278074983924074</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.1484803309559702</v>
+        <v>0.09554838326151505</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2280478051105001</v>
+        <v>0.1754503915958079</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.1075220197999122</v>
+        <v>0.03091218404264126</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.108608632389126</v>
+        <v>0.04962868577491895</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.1278859817462889</v>
+        <v>0.07162088098569633</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.06291902206904031</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0.07452577328165606</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-0.1251714325613093</v>
+        <v>0.02284419488292146</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-0.07071080772592676</v>
+        <v>0.07866046521103269</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-0.1189457866820207</v>
+        <v>0.02003067161337154</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-0.1061319525973545</v>
+        <v>0.04472033275180928</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>-0.07722082490023169</v>
+        <v>0.07211011182409528</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.004425088048725643</v>
+        <v>0.1570034719781113</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>-0.2191110522044364</v>
+        <v>0.0180482774988968</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>-0.1183042594040453</v>
+        <v>0.02933564634170345</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-0.09836595069411372</v>
+        <v>0.05185530689969101</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.04258745176413872</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.0549564976668481</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0.09618836835895887</v>
+        <v>0.1413764030044583</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.1480479770497997</v>
+        <v>0.1981797976383159</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.09535315312013798</v>
+        <v>0.1388040519305375</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.1148371507564033</v>
+        <v>0.162475300331321</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.1418757984516971</v>
+        <v>0.1914501919204304</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.2273381124703245</v>
+        <v>0.2732445864112646</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-0.00479959630014851</v>
+        <v>0.1345979732429458</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.1025960431261451</v>
+        <v>0.1482219846044359</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.1220513789510841</v>
+        <v>0.1701411258642319</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0.1613639417942665</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0.1731657127719935</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-0.1231684788300778</v>
+        <v>0.06010313801351393</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-0.07260204838189205</v>
+        <v>0.118319476392254</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>-0.1210737960210093</v>
+        <v>0.05758765142134232</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>-0.1046942702120043</v>
+        <v>0.08046491230233499</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>-0.07861763718347715</v>
+        <v>0.1113603328685366</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.003110543335474969</v>
+        <v>0.1923508747480611</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>-0.09488403118242771</v>
+        <v>0.05345131972396523</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>-0.1171214922133678</v>
+        <v>0.06742981592184363</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>-0.09777229792193683</v>
+        <v>0.08876343238746437</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0.08035780834805677</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0.09220343930881289</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2021-09</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-0.05269748639641992</v>
+        <v>0.04761243639303924</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-0.0047424105060379</v>
+        <v>0.1053480001790478</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-0.0495323130466136</v>
+        <v>0.04488628790402167</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-0.03556061435062523</v>
+        <v>0.06792176590861326</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-0.01047137178103884</v>
+        <v>0.09845891953408044</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.06468886792464577</v>
+        <v>0.181942724769328</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>-0.1017339115029216</v>
+        <v>0.0441900822399916</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>-0.04691552756434692</v>
+        <v>0.05492433775469161</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>-0.02886699801099107</v>
+        <v>0.07611744691225274</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0.06787036332191596</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>0.08015577795500736</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-0.03805553591436443</v>
+        <v>0.3029002430473683</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.00986175286764384</v>
+        <v>0.3643093715366567</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-0.03582538779240065</v>
+        <v>0.3006395842446443</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-0.01906373005076212</v>
+        <v>0.3216744107606022</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.004240869335755536</v>
+        <v>0.3568253378389514</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.08651599350009823</v>
+        <v>0.4325285129517925</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-0.09539505932100152</v>
+        <v>0.2925089941189263</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-0.03262451230377804</v>
+        <v>0.3112039157566914</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-0.01302076947597901</v>
+        <v>0.3313687519639826</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0.3239935880260043</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0.3348843469132906</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-0.1774637454608132</v>
+        <v>0.1238809413067367</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-0.130382022166731</v>
+        <v>0.1827686908880636</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-0.1770515025914181</v>
+        <v>0.1223495275810151</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-0.1582258556177266</v>
+        <v>0.1414356373989095</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-0.1358684067202581</v>
+        <v>0.1755559632428736</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>-0.05148651011775413</v>
+        <v>0.2404924233595447</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>-0.3395951122916553</v>
+        <v>0.1067075699499504</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>-0.1721736828539516</v>
+        <v>0.1317875271007257</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>-0.1524826912591693</v>
+        <v>0.1508761847453593</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>0.1440084779391643</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>0.1528727183970199</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>0.02450283324234377</v>
+        <v>0.02473520904490717</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.06945605279932865</v>
+        <v>0.08984530307160851</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.02574236646399103</v>
+        <v>0.0230281679395012</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.0438708529772059</v>
+        <v>0.04317200998599571</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.06426691659348364</v>
+        <v>0.0818202009074783</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.1097607261099147</v>
+        <v>0.1506480516926524</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>-0.3321202756168368</v>
+        <v>0.005104818642516982</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.02929681137295482</v>
+        <v>0.03369419051068995</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.0490034250141239</v>
+        <v>0.05394983603398375</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.04674609620945398</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>0.05622197642548156</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0.1425532065197164</v>
+        <v>0.1703938507836436</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.1842354967934879</v>
+        <v>0.2329024039859901</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.1446479092261767</v>
+        <v>0.1683238704152898</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.1611612483888408</v>
+        <v>0.1892853874274027</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.1794535296129987</v>
+        <v>0.2252681628007171</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.08829437398022788</v>
+        <v>0.297592867547735</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>-0.3311363032383043</v>
+        <v>0.1553631743649436</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1467985376986108</v>
+        <v>0.1788333358850688</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.1656890361048744</v>
+        <v>0.1992250604185014</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>0.1913822258783406</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>0.2019097904032547</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0.2270738393267514</v>
+        <v>0.2553201171580137</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.2715197013713341</v>
+        <v>0.3103310677944811</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.2308630444125759</v>
+        <v>0.2533962959398685</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.2459079609525535</v>
+        <v>0.2751089377732542</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.2663643643050966</v>
+        <v>0.3037704404445927</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2767216111187223</v>
+        <v>0.3742084415409008</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-0.1563205574387031</v>
+        <v>0.241044533961943</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.2317902935574254</v>
+        <v>0.2619730192567931</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.2510846438309853</v>
+        <v>0.2827459250331652</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0.2739336362797964</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>0.2842109754336681</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.1027354644855147</v>
+        <v>0.3365408384714535</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.1468919327172825</v>
+        <v>0.3849893706144007</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.1046348522977023</v>
+        <v>0.3353841708418631</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.121043873976024</v>
+        <v>0.3555352111709251</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.1417515500999002</v>
+        <v>0.3792773361993583</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.3089300420079921</v>
+        <v>0.4382152528622338</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-0.1152922333666334</v>
+        <v>0.3163874437738521</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.1075414567432567</v>
+        <v>0.3418654110925772</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.1263288851648351</v>
+        <v>0.3616999570222661</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0.3529381599340671</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>0.3610994435609922</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>0.02145466115377789</v>
+        <v>-0.02312229045965181</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.06960621129404017</v>
+        <v>0.02022681987330523</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>0.02387521057537421</v>
+        <v>-0.021909236967736</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>0.04003516586020507</v>
+        <v>-0.003334880577496748</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.06393038368689603</v>
+        <v>0.01523405434462271</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2159943493625659</v>
+        <v>0.0615657853639599</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>-0.2267310275896602</v>
+        <v>-0.05550593937250058</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.02700978927756882</v>
+        <v>-0.01930015543484413</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.0462823480869184</v>
+        <v>0.001180795756600123</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>-0.008015360726882534</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>-0.002773894163749034</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-0.02739885917757616</v>
+        <v>0.4780317896439253</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.01782780948638086</v>
+        <v>0.5264630693295475</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>-0.02156519346125414</v>
+        <v>0.4806454957981513</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>-0.008452748957453555</v>
+        <v>0.4978425097382929</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.01256410055690446</v>
+        <v>0.5208262854651194</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.09987162353673992</v>
+        <v>0.6057700311828927</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>-0.338158587188028</v>
+        <v>0.4881706380473486</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>-0.02262176661423141</v>
+        <v>0.483548250311634</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>-0.003114704957242365</v>
+        <v>0.5037485721449538</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0.4946861857351522</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>0.5094496268513183</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>-0.0315012326056799</v>
+        <v>0.5390506961180702</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.01270862235281394</v>
+        <v>0.5880556475204872</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>-0.02331818026013196</v>
+        <v>0.5421732255625863</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>-0.01285442485697873</v>
+        <v>0.5588877101984873</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.007560383798479929</v>
+        <v>0.5823408618073536</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.0912184193869051</v>
+        <v>0.667160583442609</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>-0.3397309607158505</v>
+        <v>0.548865290175667</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>-0.02698924668265242</v>
+        <v>0.5446601125248454</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>-0.007691308496097508</v>
+        <v>0.5649357370512414</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0.5557090022401832</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>0.5706810960445942</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>0.004434875404178623</v>
+        <v>0.04525216794032216</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.03594836786256726</v>
+        <v>0.1090009724800244</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>-0.00638274667147687</v>
+        <v>0.05116126015741487</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.01008690851810784</v>
+        <v>0.06653983224949382</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.0307694053120253</v>
+        <v>0.1013291754521733</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.1226743189251594</v>
+        <v>0.1947213168383227</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>-0.3123569240445936</v>
+        <v>0.05172106559161968</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>-0.003856749661183852</v>
+        <v>0.05351796417784904</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.01533998975364892</v>
+        <v>0.07598013761880193</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>0.06638164257270879</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0.08324709916733576</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>0.1270820498408712</v>
+        <v>-0.04798700003292294</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.1554903203962089</v>
+        <v>0.0102494568946281</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.1139636148621031</v>
+        <v>-0.04311766436815226</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.1294690560503807</v>
+        <v>-0.02639672309183706</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.1503467878293092</v>
+        <v>0.003354235238600175</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2367388760641572</v>
+        <v>0.09641461013663047</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>-0.1841372132843305</v>
+        <v>-0.03956555724397762</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1162386689929112</v>
+        <v>-0.04088201883928078</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.1348192693779592</v>
+        <v>-0.01851789409763527</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>-0.02824146744666121</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>-0.01182761726710524</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>0.2243735714428837</v>
+        <v>-0.1782963026246124</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0.2534423930540514</v>
+        <v>-0.1214738193324258</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.2124123629267024</v>
+        <v>-0.1719764432360556</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.2266398722109325</v>
+        <v>-0.1579850883659235</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.2481725918013759</v>
+        <v>-0.1282407662190511</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.3342730662404124</v>
+        <v>-0.0413783862673805</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>-0.0925581913005831</v>
+        <v>-0.1721716422221407</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.2133384740460622</v>
+        <v>-0.1712064592116029</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.232178347458675</v>
+        <v>-0.1500349667866955</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>-0.1587839370080999</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>-0.1436404304739876</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.339792824979006</v>
+        <v>0.1181894702195957</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.371147846971829</v>
+        <v>0.173757033273074</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.3276800044040658</v>
+        <v>0.1220245882026819</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.3416322481237726</v>
+        <v>0.137734595247146</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.365554840132196</v>
+        <v>0.1671251662656948</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.4508226512727508</v>
+        <v>0.2530602565844705</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.02455107997816795</v>
+        <v>0.125493347593237</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.3294982992528097</v>
+        <v>0.1252251081613263</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.3479401482034512</v>
+        <v>0.1456222463318141</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>0.1371341810576424</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0.1520257568754489</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>0.1479712748655347</v>
+        <v>0.1019018402948163</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>0.1798273574689987</v>
+        <v>0.154806374266328</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.135162747323895</v>
+        <v>0.1073188646786817</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>0.1497901378631617</v>
+        <v>0.1203095988575679</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.1741659614936922</v>
+        <v>0.1484803309559702</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2603087896943613</v>
+        <v>0.2280478051105001</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>-0.1677686510463499</v>
+        <v>0.1075220197999122</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1377912300224187</v>
+        <v>0.108608632389126</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.1562370065432888</v>
+        <v>0.1278859817462889</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0.1201939032911434</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0.1338757164554657</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>0.2256822547698209</v>
+        <v>-0.1251714325613093</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.2616992551613812</v>
+        <v>-0.07071080772592676</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0.2167245195764706</v>
+        <v>-0.1189457866820207</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.2266147659741689</v>
+        <v>-0.1061319525973545</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.2554081637222506</v>
+        <v>-0.07722082490023169</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.3369209298613811</v>
+        <v>0.004425088048725643</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>-0.09474181049360617</v>
+        <v>-0.2191110522044364</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.2164208487808186</v>
+        <v>-0.1183042594040453</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.2344623085606138</v>
+        <v>-0.09836595069411372</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>-0.1061064772190152</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>-0.1032818865245236</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>0.2707895778965699</v>
+        <v>0.09618836835895887</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.3087686851170282</v>
+        <v>0.1480479770497997</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.2604119107202464</v>
+        <v>0.09535315312013798</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.2712609171348483</v>
+        <v>0.1148371507564033</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.3022155991884501</v>
+        <v>0.1418757984516971</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.4697515448246242</v>
+        <v>0.2273381124703245</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.04384290788530757</v>
+        <v>-0.00479959630014851</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.2624111940048456</v>
+        <v>0.1025960431261451</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.2798199423701095</v>
+        <v>0.1220513789510841</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>0.1138987588992913</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>0.1159431539982669</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>0.09243451729896038</v>
+        <v>-0.1231684788300778</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0.1311783900244556</v>
+        <v>-0.07260204838189205</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.07889509818799435</v>
+        <v>-0.1210737960210093</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.09296637299274181</v>
+        <v>-0.1046942702120043</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.1245185555981822</v>
+        <v>-0.07861763718347715</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.3343838066637024</v>
+        <v>0.003110543335474969</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>-0.09727653153514679</v>
+        <v>-0.09488403118242771</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.08413281306035431</v>
+        <v>-0.1171214922133678</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.1017008200523114</v>
+        <v>-0.09777229792193683</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>-0.1052863593027979</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>-0.08964705651230198</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>-0.05755090800632171</v>
+        <v>-0.05269748639641992</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>-0.01870151280963928</v>
+        <v>-0.0047424105060379</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>-0.07164894233579724</v>
+        <v>-0.0495323130466136</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>-0.05688864045481946</v>
+        <v>-0.03556061435062523</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>-0.02537870569647551</v>
+        <v>-0.01047137178103884</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1872987764511871</v>
+        <v>0.06468886792464577</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>-0.2489680373392206</v>
+        <v>-0.1017339115029216</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>-0.06596033112450343</v>
+        <v>-0.04691552756434692</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>-0.04818008288782043</v>
+        <v>-0.02886699801099107</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>-0.03533763992513438</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>-0.02953686280381659</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>0.03418337015600794</v>
+        <v>-0.03805553591436443</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>0.07364950197161842</v>
+        <v>0.00986175286764384</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.02173743000959172</v>
+        <v>-0.03582538779240065</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0.03462291955304509</v>
+        <v>-0.01906373005076212</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.0668790588288341</v>
+        <v>0.004240869335755536</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.2765416077093975</v>
+        <v>0.08651599350009823</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>-0.157592126027824</v>
+        <v>-0.09539505932100152</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.02598619805543485</v>
+        <v>-0.03262451230377804</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.04357477189070409</v>
+        <v>-0.01302076947597901</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>-0.0204572223499882</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>-0.01481848657275424</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>0.07645695936170779</v>
+        <v>-0.1774637454608132</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>0.1188087949600986</v>
+        <v>-0.130382022166731</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.06318754395384787</v>
+        <v>-0.1770515025914181</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.07632002755480706</v>
+        <v>-0.1582258556177266</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.1116214963305073</v>
+        <v>-0.1358684067202581</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.319860853450002</v>
+        <v>-0.05148651011775413</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>-0.1143504050723992</v>
+        <v>-0.3395951122916553</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.06909918187962724</v>
+        <v>-0.1721736828539516</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.08624720942447547</v>
+        <v>-0.1524826912591693</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>-0.1601577772404909</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>-0.1660810587866086</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0.1503984391096282</v>
+        <v>0.02450283324234377</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0.1975324299104744</v>
+        <v>0.06945605279932865</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.1397312176239113</v>
+        <v>0.02574236646399103</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.1492001120863514</v>
+        <v>0.0438708529772059</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.1896393732347197</v>
+        <v>0.06426691659348364</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.3919158037100189</v>
+        <v>0.1097607261099147</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-0.04211910700252299</v>
+        <v>-0.3321202756168368</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1443373111955725</v>
+        <v>0.02929681137295482</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.1607696613396271</v>
+        <v>0.0490034250141239</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>0.04149152194115793</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>0.009308856550723298</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>0.1751262064072822</v>
+        <v>0.1425532065197164</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0.2253320222733451</v>
+        <v>0.1842354967934879</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0.1626858522485338</v>
+        <v>0.1446479092261767</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.1784410882096432</v>
+        <v>0.1611612483888408</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.2173966901069373</v>
+        <v>0.1794535296129987</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.4195671500243737</v>
+        <v>0.08829437398022788</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>-0.01321568898742414</v>
+        <v>-0.3311363032383043</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.1740370046444761</v>
+        <v>0.1467985376986108</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.1898085724922207</v>
+        <v>0.1656890361048744</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>0.1585756865529264</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>0.09796633723184768</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>0.1004129450455565</v>
+        <v>0.2270738393267514</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.1530290992496533</v>
+        <v>0.2715197013713341</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0.09004319213753387</v>
+        <v>0.2308630444125759</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0.1120270202185993</v>
+        <v>0.2459079609525535</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1454686506607742</v>
+        <v>0.2663643643050966</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.3396201890591344</v>
+        <v>0.2767216111187223</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>-0.07960882643226981</v>
+        <v>-0.1563205574387031</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1075190003812749</v>
+        <v>0.2317902935574254</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.1221312596086539</v>
+        <v>0.2510846438309853</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>0.2440264461166294</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>0.2050005446040824</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>0.04592913176516697</v>
+        <v>0.1027354644855147</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0.09929845131062562</v>
+        <v>0.1468919327172825</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.03609905996517689</v>
+        <v>0.1046348522977023</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0.05760953430026511</v>
+        <v>0.121043873976024</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.09162477085962516</v>
+        <v>0.1417515500999002</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2871285787650001</v>
+        <v>0.3089300420079921</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>-0.1361559829161539</v>
+        <v>-0.1152922333666334</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.05315525929467917</v>
+        <v>0.1075414567432567</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.06789262438984844</v>
+        <v>0.1263288851648351</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>0.1189878813764335</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>0.1160628693473194</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>-0.05159854883966405</v>
+        <v>0.02145466115377789</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0.002282203914305093</v>
+        <v>0.06960621129404017</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>-0.06130580749367456</v>
+        <v>0.02387521057537421</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>-0.03996030014469611</v>
+        <v>0.04003516586020507</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>-0.005473934333449349</v>
+        <v>0.06393038368689603</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.190568525676118</v>
+        <v>0.2159943493625659</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>-0.2345773167872732</v>
+        <v>-0.2267310275896602</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>-0.04429534381112037</v>
+        <v>0.02700978927756882</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-0.02952743332334451</v>
+        <v>0.0462823480869184</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>0.03868273481516413</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>0.03127301018974292</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>-0.1040191562042564</v>
+        <v>-0.02739885917757616</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>-0.05237821234073309</v>
+        <v>0.01782780948638086</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>-0.1144060682772108</v>
+        <v>-0.02156519346125414</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>-0.09194702424566926</v>
+        <v>-0.008452748957453555</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>-0.05978195153332357</v>
+        <v>0.01256410055690446</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1370968635330881</v>
+        <v>0.09987162353673992</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>-0.2854814608976235</v>
+        <v>-0.338158587188028</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>-0.09726293212453711</v>
+        <v>-0.02262176661423141</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-0.08226632622942745</v>
+        <v>-0.003114704957242365</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>-0.01080548211903698</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>-0.03233870297508448</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>-0.01505082597048694</v>
+        <v>-0.0315012326056799</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>0.03447647645811784</v>
+        <v>0.01270862235281394</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>-0.02458144924067001</v>
+        <v>-0.02331818026013196</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>-0.002716299874020212</v>
+        <v>-0.01285442485697873</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.02738352700544852</v>
+        <v>0.007560383798479929</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1271365220654295</v>
+        <v>0.0912184193869051</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>-0.295339817685339</v>
+        <v>-0.3397309607158505</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>-0.008918467223546087</v>
+        <v>-0.02698924668265242</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.00629524548630665</v>
+        <v>-0.007691308496097508</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>-0.01510611816742459</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>-0.03673310311991023</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>-0.07704129635525227</v>
+        <v>0.004434875404178623</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>-0.02820186452193359</v>
+        <v>0.03594836786256726</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>-0.08802087163309504</v>
+        <v>-0.00638274667147687</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>-0.06463928255912973</v>
+        <v>0.01008690851810784</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>-0.03518908757083886</v>
+        <v>0.0307694053120253</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.06451719459589092</v>
+        <v>0.1226743189251594</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>-0.3630480472656748</v>
+        <v>-0.3123569240445936</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>-0.07107111912184821</v>
+        <v>-0.003856749661183852</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-0.05583620959239014</v>
+        <v>0.01533998975364892</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>0.0092634393744816</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>-0.01148250606684078</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>-0.08409883710779925</v>
+        <v>0.1270820498408712</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>-0.03814950283675315</v>
+        <v>0.1554903203962089</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>-0.09337332127160575</v>
+        <v>0.1139636148621031</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>-0.07215540324468418</v>
+        <v>0.1294690560503807</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>-0.04472300990485922</v>
+        <v>0.1503467878293092</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.05065063114573248</v>
+        <v>0.2367388760641572</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>-0.3587873722432316</v>
+        <v>-0.1841372132843305</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>-0.07862841855454643</v>
+        <v>0.1162386689929112</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>-0.0639735638795163</v>
+        <v>0.1348192693779592</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>0.1293706506002693</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>0.1088901589032856</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>-0.1009573135033401</v>
+        <v>0.2243735714428837</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>-0.0569536579164612</v>
+        <v>0.2534423930540514</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.1113058490844031</v>
+        <v>0.2124123629267024</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>-0.08879903068683932</v>
+        <v>0.2266398722109325</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>-0.06322577197554105</v>
+        <v>0.2481725918013759</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.03162596157319517</v>
+        <v>0.3342730662404124</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-0.3710342488905402</v>
+        <v>-0.0925581913005831</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.09591243653341296</v>
+        <v>0.2133384740460622</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>-0.08121418532621413</v>
+        <v>0.232178347458675</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>0.2268419968495295</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>0.2058080542089459</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>-0.13338555585171</v>
+        <v>0.339792824979006</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>-0.08935551050082616</v>
+        <v>0.371147846971829</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>-0.1427972568647805</v>
+        <v>0.3276800044040658</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>-0.1213499699878986</v>
+        <v>0.3416322481237726</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>-0.09564351721721226</v>
+        <v>0.365554840132196</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>-0.03006842611709932</v>
+        <v>0.4508226512727508</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>-0.4329208060512444</v>
+        <v>0.02455107997816795</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>-0.1283713977278081</v>
+        <v>0.3294982992528097</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>-0.1137204178073324</v>
+        <v>0.3479401482034512</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>0.3429663963379058</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>0.3220688825908943</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>-0.07234740038392172</v>
+        <v>0.1479712748655347</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>-0.02860531782780402</v>
+        <v>0.1798273574689987</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>-0.08289676359723115</v>
+        <v>0.135162747323895</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>-0.06006817895022595</v>
+        <v>0.1497901378631617</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>-0.03483754280340483</v>
+        <v>0.1741659614936922</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.02034987192911018</v>
+        <v>0.2603087896943613</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>-0.4240970769847269</v>
+        <v>-0.1677686510463499</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>-0.06741899360130313</v>
+        <v>0.1377912300224187</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>-0.05259825788687889</v>
+        <v>0.1562370065432888</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>0.1511800733893462</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>0.1303873171365557</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>-0.1620108821327913</v>
+        <v>0.2256822547698209</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>-0.1167966773548162</v>
+        <v>0.2616992551613812</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>-0.1725964655852718</v>
+        <v>0.2167245195764706</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>-0.1501393456834925</v>
+        <v>0.2266147659741689</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>-0.1232573842846948</v>
+        <v>0.2554081637222506</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>-0.1091608927338487</v>
+        <v>0.3369209298613811</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>-0.5116724892235487</v>
+        <v>-0.09474181049360617</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>-0.1566241185712041</v>
+        <v>0.2164208487808186</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>-0.1421271007221396</v>
+        <v>0.2344623085606138</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>0.2301829807218793</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>0.2087990262125888</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>-0.1636232400496713</v>
+        <v>0.2707895778965699</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>-0.1206770750852441</v>
+        <v>0.3087686851170282</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>-0.1739008835734971</v>
+        <v>0.2604119107202464</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>-0.1516980319144482</v>
+        <v>0.2712609171348483</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>-0.1267968740553364</v>
+        <v>0.3022155991884501</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1252950269805977</v>
+        <v>0.4697515448246242</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>-0.5191172052843427</v>
+        <v>0.04384290788530757</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>-0.1587185790551621</v>
+        <v>0.2624111940048456</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>-0.1443157227039596</v>
+        <v>0.2798199423701095</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>0.2755881167636954</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>0.2743635865713366</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>-0.008395888872077492</v>
+        <v>0.09243451729896038</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0.03261997800794536</v>
+        <v>0.1311783900244556</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>-0.01590138698237045</v>
+        <v>0.07889509818799435</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0.004022410665694953</v>
+        <v>0.09296637299274181</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.02678190777310823</v>
+        <v>0.1245185555981822</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.03884313617218478</v>
+        <v>0.3343838066637024</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>-0.4392299486139112</v>
+        <v>-0.09727653153514679</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>-0.004226818883603409</v>
+        <v>0.08413281306035431</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.0106986975367663</v>
+        <v>0.1017008200523114</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>0.09703030499180176</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>0.1047704269270617</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0.5657184693774056</v>
+        <v>-0.05755090800632171</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0.6047905643393144</v>
+        <v>-0.01870151280963928</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.5672911539638846</v>
+        <v>-0.07164894233579724</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.5770317045652348</v>
+        <v>-0.05688864045481946</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.5991692208993407</v>
+        <v>-0.02537870569647551</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.5359229342226992</v>
+        <v>0.1872987764511871</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1464262690850114</v>
+        <v>-0.2489680373392206</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.569436636542437</v>
+        <v>-0.06596033112450343</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.5835422280241681</v>
+        <v>-0.04818008288782043</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>-0.05292635613027434</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>-0.04510870935593451</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>0.8346751137727</v>
+        <v>0.03418337015600794</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>0.8713017014145411</v>
+        <v>0.07364950197161842</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>0.8378796711926826</v>
+        <v>0.02173743000959172</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>0.8463522442489326</v>
+        <v>0.03462291955304509</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.8660384528434599</v>
+        <v>0.0668790588288341</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.8026811600787453</v>
+        <v>0.2765416077093975</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.4407918581067928</v>
+        <v>-0.157592126027824</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.8376159843869582</v>
+        <v>0.02598619805543485</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.8520655037735847</v>
+        <v>0.04357477189070409</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>0.03929994692109344</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>0.04662030357186775</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>0.8736275308349518</v>
+        <v>0.07645695936170779</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>0.9106385214012321</v>
+        <v>0.1188087949600986</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.8651922269715675</v>
+        <v>0.06318754395384787</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0.8863431862178038</v>
+        <v>0.07632002755480706</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.9054068812208412</v>
+        <v>0.1116214963305073</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.8525016290510918</v>
+        <v>0.319860853450002</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.4823992182542651</v>
+        <v>-0.1143504050723992</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.8768729196673477</v>
+        <v>0.06909918187962724</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.891836475525417</v>
+        <v>0.08624720942447547</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>0.08219589958745992</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>0.08969462909363046</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>0.3914711770120119</v>
+        <v>0.1503984391096282</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>0.4299372666996996</v>
+        <v>0.1975324299104744</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.3820786398858859</v>
+        <v>0.1397312176239113</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>0.4036412967537537</v>
+        <v>0.1492001120863514</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.4244805202912913</v>
+        <v>0.1896393732347197</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3836467431411411</v>
+        <v>0.3919158037100189</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.01639127006306314</v>
+        <v>-0.04211910700252299</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.3952506797387386</v>
+        <v>0.1443373111955725</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.4097223703873874</v>
+        <v>0.1607696613396271</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>0.1576286176947944</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>0.1646005823564201</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.5086854500039641</v>
+        <v>0.1751262064072822</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.5471722536338067</v>
+        <v>0.2253320222733451</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.5006812913120728</v>
+        <v>0.1626858522485338</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.5208358579456415</v>
+        <v>0.1784410882096432</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.5417042723478223</v>
+        <v>0.2173966901069373</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.5006317828709068</v>
+        <v>0.4195671500243737</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1339651004514651</v>
+        <v>-0.01321568898742414</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.5124093889426929</v>
+        <v>0.1740370046444761</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.5269241833073459</v>
+        <v>0.1898085724922207</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>0.1852068055275511</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>0.1921309886021542</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>0.4775282759452981</v>
+        <v>0.1004129450455565</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>0.5151508313379232</v>
+        <v>0.1530290992496533</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.4678718147443421</v>
+        <v>0.09004319213753387</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.4892500671503901</v>
+        <v>0.1120270202185993</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.5098127149158553</v>
+        <v>0.1454686506607742</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.4703125142897109</v>
+        <v>0.3396201890591344</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1140873513444309</v>
+        <v>-0.07960882643226981</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.4813152016640412</v>
+        <v>0.1075190003812749</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.4952634233987556</v>
+        <v>0.1221312596086539</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>0.1153519786647092</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>0.1211825033254345</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>0.04592913176516697</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0.09929845131062562</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0.03609905996517689</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.05760953430026511</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0.09162477085962516</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0.2871285787650001</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>-0.1361559829161539</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0.05315525929467917</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>0.06789262438984844</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>0.06114703608868427</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>0.06695349197047039</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>-0.05159854883966405</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0.002282203914305093</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>-0.06130580749367456</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>-0.03996030014469611</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>-0.005473934333449349</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0.190568525676118</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>-0.2345773167872732</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>-0.04429534381112037</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>-0.02952743332334451</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>-0.03639148959311089</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>-0.03043199501586656</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>-0.1040191562042564</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>-0.05237821234073309</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>-0.1144060682772108</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>-0.09194702424566926</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>-0.05978195153332357</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0.1370968635330881</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>-0.2854814608976235</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>-0.09726293212453711</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>-0.08226632622942745</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>-0.089423886325333</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>-0.08338291870218811</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>-0.01505082597048694</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.03447647645811784</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>-0.02458144924067001</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>-0.002716299874020212</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.02738352700544852</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.1271365220654295</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>-0.295339817685339</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>-0.008918467223546087</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0.00629524548630665</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>-0.0009395292080975432</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>-0.01681278766430664</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>-0.07704129635525227</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>-0.02820186452193359</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>-0.08802087163309504</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>-0.06463928255912973</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>-0.03518908757083886</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0.06451719459589092</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>-0.3630480472656748</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>-0.07107111912184821</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>-0.05583620959239014</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>-0.06332777962192282</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>-0.07983673155825241</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>-0.08409883710779925</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>-0.03814950283675315</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>-0.09337332127160575</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>-0.07215540324468418</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>-0.04472300990485922</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0.05065063114573248</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>-0.3587873722432316</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>-0.07862841855454643</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>-0.0639735638795163</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>-0.07106070583513889</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>-0.08702653309969594</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>-0.1009573135033401</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>-0.0569536579164612</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>-0.1113058490844031</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>-0.08879903068683932</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>-0.06322577197554105</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0.03162596157319517</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>-0.3710342488905402</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>-0.09591243653341296</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>-0.08121418532621413</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>-0.08854277257134459</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>-0.1041973924826174</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>-0.13338555585171</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>-0.08935551050082616</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>-0.1427972568647805</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>-0.1213499699878986</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>-0.09564351721721226</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>-0.03006842611709932</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>-0.4329208060512444</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>-0.1283713977278081</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>-0.1137204178073324</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>-0.120928366778321</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>-0.1430680953473235</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>-0.07234740038392172</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>-0.02860531782780402</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>-0.08289676359723115</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>-0.06006817895022595</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>-0.03483754280340483</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>-0.02034987192911018</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>-0.4240970769847269</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>-0.06741899360130313</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>-0.05259825788687889</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>-0.06004050559270899</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>-0.09369104488495632</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>-0.1620108821327913</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>-0.1167966773548162</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>-0.1725964655852718</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>-0.1501393456834925</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>-0.1232573842846948</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>-0.1091608927338487</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>-0.5116724892235487</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>-0.1566241185712041</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>-0.1421271007221396</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>-0.1493649159306881</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>-0.1827094840324231</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>-0.1636232400496713</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>-0.1206770750852441</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>-0.1739008835734971</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>-0.1516980319144482</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>-0.1267968740553364</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>-0.1252950269805977</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>-0.5191172052843427</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>-0.1587185790551621</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>-0.1443157227039596</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>-0.1515373243951889</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>-0.1871269598558066</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>-0.008395888872077492</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0.03261997800794536</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>-0.01590138698237045</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.004022410665694953</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.02678190777310823</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>-0.03884313617218478</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>-0.4392299486139112</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>-0.004226818883603409</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0.0106986975367663</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>0.003521288021449102</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>-0.0480526872822925</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>0.5657184693774056</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0.6047905643393144</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0.5672911539638846</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0.5770317045652348</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.5991692208993407</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0.5359229342226992</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0.1464262690850114</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0.569436636542437</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0.5835422280241681</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>0.5778522413824405</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>0.5277032423354995</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>0.8346751137727</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>0.8713017014145411</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>0.8378796711926826</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0.8463522442489326</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0.8660384528434599</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0.8026811600787453</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0.4407918581067928</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>0.8376159843869582</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0.8520655037735847</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>0.846380940603808</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>0.7988224099798219</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>0.8736275308349518</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0.9106385214012321</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0.8651922269715675</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0.8863431862178038</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0.9054068812208412</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0.8525016290510918</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0.4823992182542651</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>0.8768729196673477</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>0.891836475525417</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>0.8842571303881122</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>0.8383131765716132</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>0.3914711770120119</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0.4299372666996996</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0.3820786398858859</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.4036412967537537</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0.4244805202912913</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0.3836467431411411</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0.01639127006306314</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>0.3952506797387386</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>0.4097223703873874</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>0.4022809847759165</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>0.3596244404414414</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>0.5086854500039641</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0.5471722536338067</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0.5006812913120728</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0.5208358579456415</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0.5417042723478223</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>0.5006317828709068</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>0.1339651004514651</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>0.5124093889426929</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>0.5269241833073459</v>
+      </c>
+      <c r="K93" s="3" t="n">
+        <v>0.5196541863425931</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>0.4770010645350797</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>0.4775282759452981</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>0.5151508313379232</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>0.4678718147443421</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0.4892500671503901</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.5098127149158553</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0.4703125142897109</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>0.1140873513444309</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0.4813152016640412</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>0.4952634233987556</v>
+      </c>
+      <c r="K94" s="3" t="n">
+        <v>0.4880068777709523</v>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>0.4467324660878609</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n">
+      <c r="B95" s="3" t="n">
         <v>0.6213667873055688</v>
       </c>
-      <c r="C77" s="3" t="n">
+      <c r="C95" s="3" t="n">
         <v>0.6585495619479685</v>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="D95" s="3" t="n">
         <v>0.6121626642262414</v>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="E95" s="3" t="n">
         <v>0.6331364820826216</v>
       </c>
-      <c r="F77" s="3" t="n">
+      <c r="F95" s="3" t="n">
         <v>0.6532741658038002</v>
       </c>
-      <c r="G77" s="3" t="n">
+      <c r="G95" s="3" t="n">
         <v>0.6137648668758385</v>
       </c>
-      <c r="H77" s="3" t="n">
+      <c r="H95" s="3" t="n">
         <v>0.2585561007190131</v>
       </c>
-      <c r="I77" s="3" t="n">
+      <c r="I95" s="3" t="n">
         <v>0.6250120609132914</v>
       </c>
-      <c r="J77" s="3" t="n">
+      <c r="J95" s="3" t="n">
         <v>0.6390114910348297</v>
+      </c>
+      <c r="K95" s="3" t="n">
+        <v>0.6317794707915544</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>0.5905371312121304</v>
       </c>
     </row>
   </sheetData>

--- a/planilhas/ipca-defasagem.xlsx
+++ b/planilhas/ipca-defasagem.xlsx
@@ -447,7 +447,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gerado em 14/10/2026</t>
+          <t>Gerado em 15/10/2026</t>
         </is>
       </c>
     </row>

--- a/planilhas/ipca-defasagem.xlsx
+++ b/planilhas/ipca-defasagem.xlsx
@@ -11133,7 +11133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11299,1341 +11299,1379 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Primeiro, as outras praças correram atrás, e correr atrás some do acumulado em doze meses. Segundo, a</t>
+          <t>Primeiro, as outras praças correram atrás, e correr atrás some do acumulado em doze meses. Segundo, e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>subvenção da MP 1.358 vale para TODO produtor e importador desde junho de 2026, Acelen inclusive: o</t>
+          <t>sobretudo, a subvenção da MP 1.358 chegou à Bahia. A Petrobras passou a descontar os R$ 0,44 por litro em</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>preço baiano também passou a ser segurado, e o controle deixou de ser controle.</t>
+          <t>29/5/2026; a Acelen, só em 13/8/2026, dois meses e meio depois. Nas duas semanas seguintes o preço de</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>bomba baiano caiu R$ 0,25 enquanto o do Brasil ficou parado, e o IPCA Gasolina de Salvador fez -4,4% em</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>É por isso que o acumulado em 12 meses por este caminho vai a zero em setembro de 2026 enquanto o</t>
+          <t>agosto, o maior recuo das dezesseis praças. A tabela da Acelen mal se mexeu nesse período: o que mudou</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>contábil ainda marca 0,8 p.p. Os dois podem estar certos ao mesmo tempo: o contábil mede o nível da</t>
+          <t>foi o que a distribuidora pagou. Ver a aba 'Acelen vs PPI' do defasagem-gasolina.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>defasagem no portão da refinaria, este mede o quanto uma praça andou diferente da outra. Quando as duas</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>estão seguradas pelo mesmo programa, a diferença some e a defasagem fica onde estava.</t>
+          <t>Ou seja, o controle recebeu o mesmo remédio que o resto do país tomava desde maio, só que de uma vez e</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>atrasado. A diferença entre as praças sumiu, e com ela o contrafactual.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>mês</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>var. Salvador %</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>praças acima de Salvador</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>impacto do mês (p.p.)</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>IPCA mês %</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>IPCA mês contrafactual %</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2022-01</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="C35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>0.07035784214690771</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>0.6103578421469078</v>
+          <t>É por isso que o acumulado em 12 meses por este caminho vai a zero em setembro de 2026 enquanto o</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2022-02</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>0.07495976781537249</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>1.084959767815372</v>
+          <t>contábil ainda marca 0,8 p.p. Os dois podem estar certos ao mesmo tempo: o contábil mede o nível da</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2022-03</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="C37" t="n">
-        <v>7</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>-0.01031607087721543</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>1.609683929122785</v>
+          <t>defasagem no portão da refinaria, este mede o quanto uma praça andou diferente da outra. Quando as duas</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2022-04</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="C38" t="n">
-        <v>15</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>-0.4156336767950466</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>0.6443663232049535</v>
+          <t>estão seguradas pelo mesmo programa, a diferença some e a defasagem fica onde estava.</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2022-05</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>0.3889659680066927</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>0.8589659680066927</v>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2022-06</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>0.3702631951740569</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>1.040263195174057</v>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>mês</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>var. Salvador %</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>praças acima de Salvador</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>impacto do mês (p.p.)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>IPCA mês %</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>IPCA mês contrafactual %</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>-16.97</v>
+        <v>-0.12</v>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-0.1094658730916288</v>
+        <v>0.07035784214690771</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.68</v>
+        <v>0.54</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-0.7894658730916289</v>
+        <v>0.6103578421469078</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-12.2</v>
+        <v>0.64</v>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>-0.03294240059681942</v>
+        <v>0.07495976781537249</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>-0.36</v>
+        <v>1.01</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>-0.3929424005968194</v>
+        <v>1.084959767815372</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-7.18</v>
+        <v>6.74</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.06540266696580335</v>
+        <v>-0.01031607087721543</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>-0.29</v>
+        <v>1.62</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>-0.2245973330341966</v>
+        <v>1.609683929122785</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>0.51</v>
+        <v>-3.9</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.0989625227344611</v>
+        <v>-0.4156336767950466</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.59</v>
+        <v>1.06</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.6889625227344611</v>
+        <v>0.6443663232049535</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>3.37</v>
+        <v>6.66</v>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.018047288181886</v>
+        <v>0.3889659680066927</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.428047288181886</v>
+        <v>0.8589659680066927</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-7.15</v>
+        <v>4.63</v>
       </c>
       <c r="C46" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>-0.2884680138042853</v>
+        <v>0.3702631951740569</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.3315319861957147</v>
+        <v>1.040263195174057</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>6.34</v>
+        <v>-16.97</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.2573702171384694</v>
+        <v>-0.1094658730916288</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.53</v>
+        <v>-0.68</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.7873702171384694</v>
+        <v>-0.7894658730916289</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>-0.8</v>
+        <v>-12.2</v>
       </c>
       <c r="C48" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>-0.0890497073151976</v>
+        <v>-0.03294240059681942</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.84</v>
+        <v>-0.36</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.7509502926848024</v>
+        <v>-0.3929424005968194</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>7.96</v>
+        <v>-7.18</v>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>-0.01368802829460854</v>
+        <v>0.06540266696580335</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>0.71</v>
+        <v>-0.29</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.6963119717053914</v>
+        <v>-0.2245973330341966</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>-1.16</v>
+        <v>0.51</v>
       </c>
       <c r="C50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>-0.03122633617868503</v>
+        <v>0.0989625227344611</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.578773663821315</v>
+        <v>0.6889625227344611</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>-8.609999999999999</v>
+        <v>3.37</v>
       </c>
       <c r="C51" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>-0.3347799858759103</v>
+        <v>0.018047288181886</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>-0.1047799858759103</v>
+        <v>0.428047288181886</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>-0.95</v>
+        <v>-7.15</v>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.01216280183053876</v>
+        <v>-0.2884680138042853</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>-0.08</v>
+        <v>0.62</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>-0.06783719816946124</v>
+        <v>0.3315319861957147</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>11.04</v>
+        <v>6.34</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0.2894984855630253</v>
+        <v>0.2573702171384694</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.12</v>
+        <v>0.53</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.4094984855630253</v>
+        <v>0.7873702171384694</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2.56</v>
+        <v>-0.8</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.06625605451240257</v>
+        <v>-0.0890497073151976</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0.23</v>
+        <v>0.84</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.2962560545124026</v>
+        <v>0.7509502926848024</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>0.78</v>
+        <v>7.96</v>
       </c>
       <c r="C55" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>-0.09897341458003038</v>
+        <v>-0.01368802829460854</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.26</v>
+        <v>0.71</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.1610265854199696</v>
+        <v>0.6963119717053914</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
         <v>-1.16</v>
       </c>
       <c r="C56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.02112403006288471</v>
+        <v>-0.03122633617868503</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.24</v>
+        <v>0.61</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.2611240300628847</v>
+        <v>0.578773663821315</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>-3.6</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.09811635484224135</v>
+        <v>-0.3347799858759103</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.1818836451577587</v>
+        <v>-0.1047799858759103</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.95</v>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>-0.01073828620756138</v>
+        <v>0.01216280183053876</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.5492617137924387</v>
+        <v>-0.06783719816946124</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>-0.93</v>
+        <v>11.04</v>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>-0.02956669361462199</v>
+        <v>0.2894984855630253</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0.42</v>
+        <v>0.12</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.390433306385378</v>
+        <v>0.4094984855630253</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>3.88</v>
+        <v>2.56</v>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.04670216161881782</v>
+        <v>0.06625605451240257</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.83</v>
+        <v>0.23</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.8767021616188178</v>
+        <v>0.2962560545124026</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.02524114212486263</v>
+        <v>-0.09897341458003038</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.1852411421248626</v>
+        <v>0.1610265854199696</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>2.37</v>
+        <v>-1.16</v>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>0.04445635687386914</v>
+        <v>0.02112403006288471</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>0.38</v>
+        <v>0.24</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.4244563568738691</v>
+        <v>0.2611240300628847</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>2.22</v>
+        <v>-3.6</v>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>0.09156682861988309</v>
+        <v>-0.09811635484224135</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>0.46</v>
+        <v>0.28</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.5515668286198832</v>
+        <v>0.1818836451577587</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.6</v>
       </c>
       <c r="C64" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>-0.04779053564224642</v>
+        <v>-0.01073828620756138</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.1622094643577536</v>
+        <v>0.5492617137924387</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.93</v>
       </c>
       <c r="C65" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.1786708224324393</v>
+        <v>-0.02956669361462199</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2013291775675607</v>
+        <v>0.390433306385378</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>4.67</v>
+        <v>3.88</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.2097822766677853</v>
+        <v>0.04670216161881782</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>-0.02</v>
+        <v>0.83</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.1897822766677853</v>
+        <v>0.8767021616188178</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>-2.32</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="C67" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>-0.114156551351909</v>
+        <v>0.02524114212486263</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0.44</v>
+        <v>0.16</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3258434486480911</v>
+        <v>0.1852411421248626</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>-0.76</v>
+        <v>2.37</v>
       </c>
       <c r="C68" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>-0.0323750054094743</v>
+        <v>0.04445635687386914</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.5276249945905258</v>
+        <v>0.4244563568738691</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>-2.2</v>
+        <v>2.22</v>
       </c>
       <c r="C69" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>-0.1051988074774702</v>
+        <v>0.09156682861988309</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.2848011925225298</v>
+        <v>0.5515668286198832</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>4.04</v>
+        <v>-0.32</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.1823881362964981</v>
+        <v>-0.04779053564224642</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0.52</v>
+        <v>0.21</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.7023881362964981</v>
+        <v>0.1622094643577536</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.48</v>
       </c>
       <c r="C71" t="n">
         <v>15</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>-0.07106086435991452</v>
+        <v>-0.1786708224324393</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.16</v>
+        <v>0.38</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.08893913564008549</v>
+        <v>0.2013291775675607</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>0.57</v>
+        <v>4.67</v>
       </c>
       <c r="C72" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>-0.1091967748496407</v>
+        <v>0.2097822766677853</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>1.31</v>
+        <v>-0.02</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>1.200803225150359</v>
+        <v>0.1897822766677853</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>-0.02</v>
+        <v>-2.32</v>
       </c>
       <c r="C73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-0.02727272599091173</v>
+        <v>-0.114156551351909</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.5327272740090884</v>
+        <v>0.3258434486480911</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>-2.21</v>
+        <v>-0.76</v>
       </c>
       <c r="C74" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.09774957019957448</v>
+        <v>-0.0323750054094743</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>0.43</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3322504298004255</v>
+        <v>0.5276249945905258</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.17</v>
+        <v>-2.2</v>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.04584689293590623</v>
+        <v>-0.1051988074774702</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.3058468929359062</v>
+        <v>0.2848011925225298</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>2.64</v>
+        <v>4.04</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.1568290877241253</v>
+        <v>0.1823881362964981</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.3968290877241253</v>
+        <v>0.7023881362964981</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>-3.86</v>
+        <v>-0.78</v>
       </c>
       <c r="C77" t="n">
         <v>15</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>-0.1728981647982739</v>
+        <v>-0.07106086435991452</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.0871018352017261</v>
+        <v>0.08893913564008549</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>1.25</v>
+        <v>0.57</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.1138332624844519</v>
+        <v>-0.1091967748496407</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>-0.11</v>
+        <v>1.31</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.003833262484451858</v>
+        <v>1.200803225150359</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.02</v>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>-0.05071199984184536</v>
+        <v>-0.02727272599091173</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.4292880001581546</v>
+        <v>0.5327272740090884</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>1.35</v>
+        <v>-2.21</v>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.05595049424009547</v>
+        <v>-0.09774957019957448</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.09</v>
+        <v>0.43</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1459504942400955</v>
+        <v>0.3322504298004255</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>-2.38</v>
+        <v>0.17</v>
       </c>
       <c r="C81" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-0.09993051483792986</v>
+        <v>0.04584689293590623</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.08006948516207013</v>
+        <v>0.3058468929359062</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>-1</v>
+        <v>2.64</v>
       </c>
       <c r="C82" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.05908088512306089</v>
+        <v>0.1568290877241253</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.2709191148769391</v>
+        <v>0.3968290877241253</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>3.35</v>
+        <v>-3.86</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.06429960621375989</v>
+        <v>-0.1728981647982739</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.3942996062137599</v>
+        <v>0.0871018352017261</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>-3.57</v>
+        <v>1.25</v>
       </c>
       <c r="C84" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>-0.1524773349539384</v>
+        <v>0.1138332624844519</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0.7</v>
+        <v>-0.11</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.5475226650460615</v>
+        <v>0.003833262484451858</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>17.37</v>
+        <v>-0.27</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.6290779171934394</v>
+        <v>-0.05071199984184536</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>0.88</v>
+        <v>0.48</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>1.509077917193439</v>
+        <v>0.4292880001581546</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>0.7</v>
+        <v>1.35</v>
       </c>
       <c r="C86" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.05920827207165286</v>
+        <v>0.05595049424009547</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>0.67</v>
+        <v>0.09</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.6107917279283471</v>
+        <v>0.1459504942400955</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>-3.45</v>
+        <v>-2.38</v>
       </c>
       <c r="C87" t="n">
         <v>14</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.1057555537760053</v>
+        <v>-0.09993051483792986</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>0.58</v>
+        <v>0.18</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.4742444462239946</v>
+        <v>0.08006948516207013</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>1.96</v>
+        <v>-1</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.109827564003661</v>
+        <v>-0.05908088512306089</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.269827564003661</v>
+        <v>0.2709191148769391</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>-3.42</v>
+        <v>3.35</v>
       </c>
       <c r="C89" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.1077737113809358</v>
+        <v>0.06429960621375989</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>-0.03777371138093584</v>
+        <v>0.3942996062137599</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>-4.36</v>
+        <v>-3.57</v>
       </c>
       <c r="C90" t="n">
         <v>15</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.1930562569446283</v>
+        <v>-0.1524773349539384</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>-0.32</v>
+        <v>0.7</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>-0.5130562569446283</v>
+        <v>0.5475226650460615</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0.6290779171934394</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>1.509077917193439</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C92" t="n">
+        <v>12</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>-0.05920827207165286</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0.6107917279283471</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="C93" t="n">
+        <v>14</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>-0.1057555537760053</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0.4742444462239946</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>0.109827564003661</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.269827564003661</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="C95" t="n">
+        <v>14</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>-0.1077737113809358</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>-0.03777371138093584</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="C96" t="n">
+        <v>15</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>-0.1930562569446283</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>-0.5130562569446283</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B91" s="3" t="n">
+      <c r="B97" s="3" t="n">
         <v>-0.37</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C97" t="n">
         <v>13</v>
       </c>
-      <c r="D91" s="3" t="n">
+      <c r="D97" s="3" t="n">
         <v>-0.07940519098689489</v>
       </c>
-      <c r="E91" s="3" t="n">
+      <c r="E97" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="F91" s="3" t="n">
+      <c r="F97" s="3" t="n">
         <v>0.740594809013105</v>
       </c>
     </row>
@@ -13562,7 +13600,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>igualmente segurado, que é o caso desde a subvenção de junho de 2026.</t>
+          <t>igualmente segurado, que é o caso desde 13/8/2026, quando a subvenção da MP 1.358 chegou à Acelen.</t>
         </is>
       </c>
     </row>

--- a/planilhas/ipca-defasagem.xlsx
+++ b/planilhas/ipca-defasagem.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contrafactual Salvador" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Praças e pesos" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IPCA 12 meses" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidade" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IPCA 12m desde o choque" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidade" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -727,150 +728,157 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>IPCA 12m desde o choque | O mesmo, contando o contrafactual só de 2026-03 em diante</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>Sensibilidade | O mesmo cálculo com a margem escalando junto</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-    </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="A48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>TRÊS ESTIMATIVAS, E ELAS NÃO BATEM</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>1. CONTÁBIL. Supõe que R$ 1,00 na refinaria vira R$ 0,70 na bomba, porque 70% do litro é gasolina A.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Nada é estimado. Supõe repasse integral e imediato, e por isso é TETO.</t>
+          <t>1. CONTÁBIL. Supõe que R$ 1,00 na refinaria vira R$ 0,70 na bomba, porque 70% do litro é gasolina A.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2. BAHIA. MEDE quanto do repasse aparece, usando o preço de bomba baiano (Acelen, que segue o PPI)</t>
+          <t xml:space="preserve">   Nada é estimado. Supõe repasse integral e imediato, e por isso é TETO.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">   como controle. Acha R$ 0,26 por real de defasagem, não R$ 0,70. É PISO: a Acelen não atende a</t>
+          <t>2. BAHIA. MEDE quanto do repasse aparece, usando o preço de bomba baiano (Acelen, que segue o PPI)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Bahia inteira, não segue o PPI perfeitamente e também recebeu as subvenções de 2026, que encolhem</t>
+          <t xml:space="preserve">   como controle. Acha R$ 0,26 por real de defasagem, não R$ 0,70. É PISO: a Acelen não atende a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">   o próprio spread que serve de medida.</t>
+          <t xml:space="preserve">   Bahia inteira, não segue o PPI perfeitamente e também recebeu as subvenções de 2026, que encolhem</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3. SALVADOR (FGV). Compara a VARIAÇÃO do IPCA Gasolina de cada praça com a de Salvador e imputa a</t>
+          <t xml:space="preserve">   o próprio spread que serve de medida.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">   diferença à defasagem. Não é ideia nossa: é o método de Francisco Pessoa Faria no Blog do IBRE,</t>
+          <t>3. SALVADOR (FGV). Compara a VARIAÇÃO do IPCA Gasolina de cada praça com a de Salvador e imputa a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">   'Impacto da defasagem da gasolina no IPCA e reflexos de sua subvenção nos resultados da Petrobras'.</t>
+          <t xml:space="preserve">   diferença à defasagem. Não é ideia nossa: é o método de Francisco Pessoa Faria no Blog do IBRE,</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ele roda a conta uma vez, no bimestre mar-abr/2026, e acha 0,59 p.p.; aqui ela roda todo mês. A aba</t>
+          <t xml:space="preserve">   'Impacto da defasagem da gasolina no IPCA e reflexos de sua subvenção nos resultados da Petrobras'.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Ele roda a conta uma vez, no bimestre mar-abr/2026, e acha 0,59 p.p.; aqui ela roda todo mês. A aba</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t xml:space="preserve">   'Praças e pesos' reproduz a tabela T.2 dele para mostrar que é a mesma conta.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-    </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>A 2 e a 3 usam a mesma intuição (a Bahia como mercado sem defasagem) por caminhos diferentes: a 2</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>compara NÍVEL de preço em R$/l e por isso desconta um spread estrutural; a 3 compara VARIAÇÃO, onde</t>
+          <t>A 2 e a 3 usam a mesma intuição (a Bahia como mercado sem defasagem) por caminhos diferentes: a 2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>compara NÍVEL de preço em R$/l e por isso desconta um spread estrutural; a 3 compara VARIAÇÃO, onde</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>diferença permanente de nível some sozinha. A largura entre as três é a sua incerteza honesta.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
-    </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
+      <c r="A65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
         <is>
           <t>ATENÇÃO — a tabela mais recente da Petrobras é de 01/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Depois dessa data o preço segue valendo até mudar. Reajuste que ainda não apareceu não está aqui.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr"/>
-    </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Fontes: PPI e preços de revenda da ANP; tabela de preços da Petrobras; IPCA da tabela 7060 do</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
+        <is>
+          <t>Fontes: PPI e preços de revenda da ANP; tabela de preços da Petrobras; IPCA da tabela 7060 do</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>SIDRA (IBGE); teor de anidro pela legislação (CNPE e MAPA).</t>
         </is>
@@ -15206,6 +15214,2077 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H99"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>O IPCA em 12 meses contando o contrafactual só a partir de 2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A aba 'IPCA 12 meses' pergunta: e se a defasagem não existisse nos últimos doze meses? Esta pergunta</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>outra coisa: e se ela não existisse A PARTIR DO CHOQUE, e antes dele tudo tivesse sido como foi?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Os meses anteriores a 2026-03 entram com o IPCA observado; os de lá para cá, com o contrafactual. Assim o</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>represamento do choque não fica diluído por meses que respondiam a outra conjuntura. É o espírito do</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>artigo da FGV, que roda a conta só no bimestre março-abril de 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>O RISCO, E ELE É REAL: escolher a data olhando a série é selecionar pelo resultado. Os meses que ficam</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>de fora são justamente os de contribuição negativa, e o número sobe sozinho. Por isso março de 2026 não</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>foi escolhido pelo gráfico: é o mês em que o PPI salta. Em Paulínia ele sai de R$ 2,573 em fevereiro para</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>R$ 3,630 em março, enquanto a tabela da Petrobras fica em R$ 2,5808, onde estava desde 27/1/2026 e onde</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ficaria até maio. O choque está no PPI, e a data vem dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>E a tabela de baixo varre o corte mês a mês, para você ver quanto a escolha decide. Ela anda MUITO:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cortando em março o contábil dá +0,70 p.p., cortando em abril dá +0,08. Quase todo o efeito está num mês só.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Isso não é defeito da conta, é o que a conta mede. O efeito no acumulado em doze meses é a MUDANÇA do</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>represamento, não o nível dele. Março é o mês em que a defasagem abre; quem começa a contar em abril já</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>encontra a defasagem aberta nas duas pontas da comparação, e por isso não vê nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A consequência para quem for citar o número: ele é 'o efeito de a defasagem TER ABERTO em março', não</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>'o efeito de a defasagem existir'. Para o segundo, a coluna certa é 'nível represado' da aba Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mensal, que em setembro de 2026 está em 0,63 p.p. e não depende de data de corte nenhuma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>mês</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>IPCA 12m observado %</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>contrafactual contábil %</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>contrafactual Bahia %</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>contrafactual Salvador %</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>efeito contábil (p.p.)</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>efeito Bahia (p.p.)</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>efeito Salvador (p.p.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>10.0610548932579</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>10.0610548932579</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>10.0610548932579</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>10.0610548932579</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>10.3794359996823</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>10.3794359996823</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>10.3794359996823</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>10.3794359996823</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>10.54359340003879</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>10.54359340003879</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>10.54359340003879</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>10.54359340003879</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>11.299315974556</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>11.299315974556</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>11.299315974556</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>11.299315974556</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>12.13148113237592</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>12.13148113237592</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>12.13148113237592</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>12.13148113237592</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>11.73113070881493</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>11.73113070881493</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>11.73113070881493</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>11.73113070881493</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>11.88672961759074</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>11.88672961759074</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>11.88672961759074</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>11.88672961759074</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>10.06923519828753</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>10.06923519828753</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>10.06923519828753</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>10.06923519828753</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>8.727060525006136</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>8.727060525006136</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>8.727060525006136</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>8.727060525006136</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>7.168596332032062</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>7.168596332032062</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>7.168596332032062</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>7.168596332032062</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>6.470015852238076</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>6.470015852238076</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>6.470015852238076</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>6.470015852238076</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>5.900488278585692</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>5.900488278585692</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>5.900488278585692</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>5.900488278585692</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>5.784841959607756</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>5.784841959607756</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>5.784841959607756</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>5.784841959607756</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>5.774320292414625</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>5.774320292414625</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>5.774320292414625</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>5.774320292414625</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>5.596301933344128</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>5.596301933344128</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>5.596301933344128</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>5.596301933344128</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>4.65069442734789</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>4.65069442734789</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>4.65069442734789</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>4.65069442734789</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>4.184705782064824</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>4.184705782064824</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>4.184705782064824</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>4.184705782064824</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>3.935832194051536</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>3.935832194051536</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>3.935832194051536</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>3.935832194051536</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>3.161501468457617</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>3.161501468457617</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>3.161501468457617</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>3.161501468457617</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>3.992443888662711</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>3.992443888662711</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>3.992443888662711</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>3.992443888662711</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>4.608216087521688</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>4.608216087521688</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>4.608216087521688</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>4.608216087521688</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>5.185234629775626</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>5.185234629775626</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>5.185234629775626</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>5.185234629775626</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>4.819245643589931</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>4.819245643589931</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>4.819245643589931</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>4.819245643589931</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>4.683537029570672</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>4.683537029570672</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>4.683537029570672</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>4.683537029570672</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>4.621113930566789</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>4.621113930566789</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>4.621113930566789</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>4.621113930566789</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>4.506637430692439</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>4.506637430692439</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>4.506637430692439</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>4.506637430692439</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>4.496273821268559</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>4.496273821268559</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>4.496273821268559</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>4.496273821268559</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>3.925596126881703</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>3.925596126881703</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>3.925596126881703</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>3.925596126881703</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>3.688016491565316</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>3.688016491565316</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>3.688016491565316</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>3.688016491565316</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>3.92595167856582</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>3.92595167856582</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>3.92595167856582</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>3.92595167856582</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>4.227578239682583</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>4.227578239682583</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>4.227578239682583</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>4.227578239682583</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>4.498245142821999</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>4.498245142821999</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>4.498245142821999</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>4.498245142821999</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>4.237599016056492</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>4.237599016056492</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>4.237599016056492</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>4.237599016056492</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>4.424740127395888</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>4.424740127395888</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>4.424740127395888</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>4.424740127395888</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>4.758099233947855</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>4.758099233947855</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>4.758099233947855</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>4.758099233947855</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>4.87301138907088</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>4.87301138907088</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>4.87301138907088</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>4.87301138907088</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>4.831295791859591</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>4.831295791859591</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>4.831295791859591</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>4.831295791859591</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>4.559874392677332</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>4.559874392677332</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>4.559874392677332</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>4.559874392677332</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>5.057630414778758</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>5.057630414778758</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>5.057630414778758</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>5.057630414778758</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>5.477189641674851</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>5.477189641674851</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>5.477189641674851</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>5.477189641674851</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>5.52972858849774</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>5.52972858849774</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>5.52972858849774</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>5.52972858849774</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>5.319635559255276</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>5.319635559255276</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>5.319635559255276</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>5.319635559255276</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>5.35116523759851</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>5.35116523759851</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>5.35116523759851</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>5.35116523759851</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>5.225222422012621</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>5.225222422012621</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>5.225222422012621</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>5.225222422012621</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>5.130500777503921</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>5.130500777503921</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>5.130500777503921</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>5.130500777503921</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>5.172368758697643</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>5.172368758697643</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>5.172368758697643</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>5.172368758697643</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>4.680811347037062</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>4.680811347037062</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>4.680811347037062</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>4.680811347037062</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>4.461835648432833</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>4.461835648432833</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>4.461835648432833</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>4.461835648432833</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>4.264384904568952</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>4.264384904568952</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>4.264384904568952</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>4.264384904568952</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>4.44135121281346</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>4.44135121281346</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>4.44135121281346</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>4.44135121281346</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>3.812496961112588</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>3.812496961112588</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>3.812496961112588</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>3.812496961112588</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>4.142846991219562</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>4.759406247070297</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>4.373166150937546</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>4.792271706483553</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0.6165592558507349</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0.2303191597179843</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>0.6494247152639909</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>4.39171967147336</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>5.249294436370278</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>4.71778514034904</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>4.980916293512805</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0.8575747648969179</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0.3260654688756803</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>0.5891966220394451</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>4.724906887660008</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>5.611456542936688</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>5.062685247756948</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>5.205248811719421</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.8865496552766805</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.3377783600969408</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0.4803419240594131</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>4.641327552554153</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>5.108953246822145</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>4.80827557603456</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>5.236553842569913</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0.4676256942679924</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0.1669480234804066</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>0.5952262900157601</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>4.44302461783459</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>5.024469608744919</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>4.654371701684279</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>4.923999691256942</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0.5814449909103292</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0.2113470838496889</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>0.4809750734223517</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>4.223452737068278</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>4.780929656596666</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>4.430692099619438</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>4.500631240168573</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0.557476919528388</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0.2072393625511593</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>0.2771785031002949</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>4.576119675071877</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>5.27333430542396</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>4.839858211590276</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>4.771653553462518</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0.6972146303520832</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0.2637385365183986</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>0.1955338783906413</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>Sensibilidade à data de corte</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>O mesmo efeito, no último mês disponível, mudando só o mês em que o contrafactual começa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>corte</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>até</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>efeito contábil (p.p.)</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>efeito Bahia (p.p.)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>efeito Salvador (p.p.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0.7998821623593111</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0.3008129217675348</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>-0.003640950315886293</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0.8346004372976612</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0.313570975286348</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>-0.06206449954266891</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0.7689093217567278</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0.2895200110215157</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0.0422933750593435</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>0.8645159525793034</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>0.3247744007882414</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0.1039358582213268</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0.8670809847609817</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0.325709506093963</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0.03689135095714668</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>0.6972146303520832</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.2637385365183986</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0.1955338783906413</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0.07763066185193512</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.03238953237565401</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>-0.4537630608652865</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>-0.1605560122005079</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>-0.06270703792539134</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>-0.3924882740031777</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.1864966761041753</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.07332343078234604</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.2828283537525733</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/planilhas/ipca-defasagem.xlsx
+++ b/planilhas/ipca-defasagem.xlsx
@@ -15214,7 +15214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15285,45 +15285,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>de fora são justamente os de contribuição negativa, e o número sobe sozinho. Por isso março de 2026 não</t>
+          <t>de fora são justamente os de contribuição negativa, e o número sobe sozinho.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>foi escolhido pelo gráfico: é o mês em que o PPI salta. Em Paulínia ele sai de R$ 2,573 em fevereiro para</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R$ 3,630 em março, enquanto a tabela da Petrobras fica em R$ 2,5808, onde estava desde 27/1/2026 e onde</t>
+          <t>Por isso o corte vem de fora dos dados: março de 2026 é quando começa a guerra no Oriente Médio. A série</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ficaria até maio. O choque está no PPI, e a data vem dele.</t>
+          <t>confirma a data em vez de escolhê-la. O PPI de Paulínia passa fevereiro inteiro parado entre R$ 2,46 e</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R$ 2,60, e aí faz +15,7% na semana encerrada em 6/3, +16,4% na seguinte e +13,2% na outra, chegando a</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E a tabela de baixo varre o corte mês a mês, para você ver quanto a escolha decide. Ela anda MUITO:</t>
+          <t>R$ 4,04 em 27/3: 55% em quatro semanas. A tabela da Petrobras fica em R$ 2,5808 o tempo todo, onde</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cortando em março o contábil dá +0,70 p.p., cortando em abril dá +0,08. Quase todo o efeito está num mês só.</t>
+          <t>estava desde 27/1/2026 e onde ficaria até maio.</t>
         </is>
       </c>
     </row>
@@ -15333,194 +15333,127 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Isso não é defeito da conta, é o que a conta mede. O efeito no acumulado em doze meses é a MUDANÇA do</t>
+          <t>E a tabela de baixo varre o corte mês a mês, para você ver quanto a escolha decide. Ela anda MUITO:</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>represamento, não o nível dele. Março é o mês em que a defasagem abre; quem começa a contar em abril já</t>
+          <t>cortando em março o contábil dá +0,70 p.p., cortando em abril dá +0,08. Quase todo o efeito está num mês só.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>encontra a defasagem aberta nas duas pontas da comparação, e por isso não vê nada.</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Isso não é defeito da conta, é o que a conta mede. O efeito no acumulado em doze meses é a MUDANÇA do</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A consequência para quem for citar o número: ele é 'o efeito de a defasagem TER ABERTO em março', não</t>
+          <t>represamento, não o nível dele. Março é o mês em que a defasagem abre; quem começa a contar em abril já</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>encontra a defasagem aberta nas duas pontas da comparação, e por isso não vê nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A consequência para quem for citar o número: ele é 'o efeito de a defasagem TER ABERTO em março', não</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>'o efeito de a defasagem existir'. Para o segundo, a coluna certa é 'nível represado' da aba Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>mensal, que em setembro de 2026 está em 0,63 p.p. e não depende de data de corte nenhuma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>mês</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>IPCA 12m observado %</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>contrafactual contábil %</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>contrafactual Bahia %</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>contrafactual Salvador %</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>efeito contábil (p.p.)</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>efeito Bahia (p.p.)</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>efeito Salvador (p.p.)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2021-12</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>10.0610548932579</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>10.0610548932579</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>10.0610548932579</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>10.0610548932579</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>0</v>
+          <t>mensal, que em setembro de 2026 está em 0,63 p.p. e não depende de data de corte nenhuma.</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2022-01</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>10.3794359996823</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>10.3794359996823</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>10.3794359996823</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>10.3794359996823</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2022-02</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>10.54359340003879</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>10.54359340003879</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>10.54359340003879</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>10.54359340003879</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>0</v>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>mês</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>IPCA 12m observado %</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>contrafactual contábil %</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>contrafactual Bahia %</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>contrafactual Salvador %</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>efeito contábil (p.p.)</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>efeito Bahia (p.p.)</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>efeito Salvador (p.p.)</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>11.299315974556</v>
+        <v>10.0610548932579</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11.299315974556</v>
+        <v>10.0610548932579</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>11.299315974556</v>
+        <v>10.0610548932579</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>11.299315974556</v>
+        <v>10.0610548932579</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>0</v>
@@ -15535,20 +15468,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>12.13148113237592</v>
+        <v>10.3794359996823</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>12.13148113237592</v>
+        <v>10.3794359996823</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>12.13148113237592</v>
+        <v>10.3794359996823</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>12.13148113237592</v>
+        <v>10.3794359996823</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
@@ -15563,20 +15496,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>11.73113070881493</v>
+        <v>10.54359340003879</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>11.73113070881493</v>
+        <v>10.54359340003879</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>11.73113070881493</v>
+        <v>10.54359340003879</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>11.73113070881493</v>
+        <v>10.54359340003879</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>0</v>
@@ -15591,20 +15524,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>11.88672961759074</v>
+        <v>11.299315974556</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>11.88672961759074</v>
+        <v>11.299315974556</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>11.88672961759074</v>
+        <v>11.299315974556</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>11.88672961759074</v>
+        <v>11.299315974556</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>0</v>
@@ -15619,20 +15552,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>10.06923519828753</v>
+        <v>12.13148113237592</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>10.06923519828753</v>
+        <v>12.13148113237592</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>10.06923519828753</v>
+        <v>12.13148113237592</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>10.06923519828753</v>
+        <v>12.13148113237592</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
@@ -15647,20 +15580,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>8.727060525006136</v>
+        <v>11.73113070881493</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>8.727060525006136</v>
+        <v>11.73113070881493</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>8.727060525006136</v>
+        <v>11.73113070881493</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>8.727060525006136</v>
+        <v>11.73113070881493</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>0</v>
@@ -15675,20 +15608,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>7.168596332032062</v>
+        <v>11.88672961759074</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>7.168596332032062</v>
+        <v>11.88672961759074</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>7.168596332032062</v>
+        <v>11.88672961759074</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>7.168596332032062</v>
+        <v>11.88672961759074</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
@@ -15703,20 +15636,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>6.470015852238076</v>
+        <v>10.06923519828753</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>6.470015852238076</v>
+        <v>10.06923519828753</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>6.470015852238076</v>
+        <v>10.06923519828753</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>6.470015852238076</v>
+        <v>10.06923519828753</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>0</v>
@@ -15731,20 +15664,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>5.900488278585692</v>
+        <v>8.727060525006136</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>5.900488278585692</v>
+        <v>8.727060525006136</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.900488278585692</v>
+        <v>8.727060525006136</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>5.900488278585692</v>
+        <v>8.727060525006136</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>0</v>
@@ -15759,20 +15692,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>5.784841959607756</v>
+        <v>7.168596332032062</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5.784841959607756</v>
+        <v>7.168596332032062</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.784841959607756</v>
+        <v>7.168596332032062</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>5.784841959607756</v>
+        <v>7.168596332032062</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
@@ -15787,20 +15720,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>5.774320292414625</v>
+        <v>6.470015852238076</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>5.774320292414625</v>
+        <v>6.470015852238076</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>5.774320292414625</v>
+        <v>6.470015852238076</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>5.774320292414625</v>
+        <v>6.470015852238076</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
@@ -15815,20 +15748,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>5.596301933344128</v>
+        <v>5.900488278585692</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>5.596301933344128</v>
+        <v>5.900488278585692</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>5.596301933344128</v>
+        <v>5.900488278585692</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>5.596301933344128</v>
+        <v>5.900488278585692</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>0</v>
@@ -15843,20 +15776,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>4.65069442734789</v>
+        <v>5.784841959607756</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>4.65069442734789</v>
+        <v>5.784841959607756</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>4.65069442734789</v>
+        <v>5.784841959607756</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>4.65069442734789</v>
+        <v>5.784841959607756</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>0</v>
@@ -15871,20 +15804,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>4.184705782064824</v>
+        <v>5.774320292414625</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>4.184705782064824</v>
+        <v>5.774320292414625</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>4.184705782064824</v>
+        <v>5.774320292414625</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>4.184705782064824</v>
+        <v>5.774320292414625</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>0</v>
@@ -15899,20 +15832,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>3.935832194051536</v>
+        <v>5.596301933344128</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>3.935832194051536</v>
+        <v>5.596301933344128</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>3.935832194051536</v>
+        <v>5.596301933344128</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>3.935832194051536</v>
+        <v>5.596301933344128</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>0</v>
@@ -15927,20 +15860,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>3.161501468457617</v>
+        <v>4.65069442734789</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>3.161501468457617</v>
+        <v>4.65069442734789</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>3.161501468457617</v>
+        <v>4.65069442734789</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>3.161501468457617</v>
+        <v>4.65069442734789</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>0</v>
@@ -15955,20 +15888,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>3.992443888662711</v>
+        <v>4.184705782064824</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>3.992443888662711</v>
+        <v>4.184705782064824</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>3.992443888662711</v>
+        <v>4.184705782064824</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>3.992443888662711</v>
+        <v>4.184705782064824</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>0</v>
@@ -15983,20 +15916,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>4.608216087521688</v>
+        <v>3.935832194051536</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>4.608216087521688</v>
+        <v>3.935832194051536</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>4.608216087521688</v>
+        <v>3.935832194051536</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>4.608216087521688</v>
+        <v>3.935832194051536</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>0</v>
@@ -16011,20 +15944,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.185234629775626</v>
+        <v>3.161501468457617</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.185234629775626</v>
+        <v>3.161501468457617</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.185234629775626</v>
+        <v>3.161501468457617</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>5.185234629775626</v>
+        <v>3.161501468457617</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -16039,20 +15972,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>4.819245643589931</v>
+        <v>3.992443888662711</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>4.819245643589931</v>
+        <v>3.992443888662711</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>4.819245643589931</v>
+        <v>3.992443888662711</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>4.819245643589931</v>
+        <v>3.992443888662711</v>
       </c>
       <c r="F49" s="3" t="n">
         <v>0</v>
@@ -16067,20 +16000,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>4.683537029570672</v>
+        <v>4.608216087521688</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>4.683537029570672</v>
+        <v>4.608216087521688</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>4.683537029570672</v>
+        <v>4.608216087521688</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>4.683537029570672</v>
+        <v>4.608216087521688</v>
       </c>
       <c r="F50" s="3" t="n">
         <v>0</v>
@@ -16095,20 +16028,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>4.621113930566789</v>
+        <v>5.185234629775626</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>4.621113930566789</v>
+        <v>5.185234629775626</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>4.621113930566789</v>
+        <v>5.185234629775626</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>4.621113930566789</v>
+        <v>5.185234629775626</v>
       </c>
       <c r="F51" s="3" t="n">
         <v>0</v>
@@ -16123,20 +16056,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>4.506637430692439</v>
+        <v>4.819245643589931</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>4.506637430692439</v>
+        <v>4.819245643589931</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>4.506637430692439</v>
+        <v>4.819245643589931</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>4.506637430692439</v>
+        <v>4.819245643589931</v>
       </c>
       <c r="F52" s="3" t="n">
         <v>0</v>
@@ -16151,20 +16084,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>4.496273821268559</v>
+        <v>4.683537029570672</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>4.496273821268559</v>
+        <v>4.683537029570672</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>4.496273821268559</v>
+        <v>4.683537029570672</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>4.496273821268559</v>
+        <v>4.683537029570672</v>
       </c>
       <c r="F53" s="3" t="n">
         <v>0</v>
@@ -16179,20 +16112,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>3.925596126881703</v>
+        <v>4.621113930566789</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>3.925596126881703</v>
+        <v>4.621113930566789</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>3.925596126881703</v>
+        <v>4.621113930566789</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>3.925596126881703</v>
+        <v>4.621113930566789</v>
       </c>
       <c r="F54" s="3" t="n">
         <v>0</v>
@@ -16207,20 +16140,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>3.688016491565316</v>
+        <v>4.506637430692439</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>3.688016491565316</v>
+        <v>4.506637430692439</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>3.688016491565316</v>
+        <v>4.506637430692439</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>3.688016491565316</v>
+        <v>4.506637430692439</v>
       </c>
       <c r="F55" s="3" t="n">
         <v>0</v>
@@ -16235,20 +16168,20 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>3.92595167856582</v>
+        <v>4.496273821268559</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>3.92595167856582</v>
+        <v>4.496273821268559</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>3.92595167856582</v>
+        <v>4.496273821268559</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>3.92595167856582</v>
+        <v>4.496273821268559</v>
       </c>
       <c r="F56" s="3" t="n">
         <v>0</v>
@@ -16263,20 +16196,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>4.227578239682583</v>
+        <v>3.925596126881703</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>4.227578239682583</v>
+        <v>3.925596126881703</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>4.227578239682583</v>
+        <v>3.925596126881703</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>4.227578239682583</v>
+        <v>3.925596126881703</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>0</v>
@@ -16291,20 +16224,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>4.498245142821999</v>
+        <v>3.688016491565316</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>4.498245142821999</v>
+        <v>3.688016491565316</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>4.498245142821999</v>
+        <v>3.688016491565316</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>4.498245142821999</v>
+        <v>3.688016491565316</v>
       </c>
       <c r="F58" s="3" t="n">
         <v>0</v>
@@ -16319,20 +16252,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>4.237599016056492</v>
+        <v>3.92595167856582</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>4.237599016056492</v>
+        <v>3.92595167856582</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>4.237599016056492</v>
+        <v>3.92595167856582</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>4.237599016056492</v>
+        <v>3.92595167856582</v>
       </c>
       <c r="F59" s="3" t="n">
         <v>0</v>
@@ -16347,20 +16280,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>4.424740127395888</v>
+        <v>4.227578239682583</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>4.424740127395888</v>
+        <v>4.227578239682583</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>4.424740127395888</v>
+        <v>4.227578239682583</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>4.424740127395888</v>
+        <v>4.227578239682583</v>
       </c>
       <c r="F60" s="3" t="n">
         <v>0</v>
@@ -16375,20 +16308,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>4.758099233947855</v>
+        <v>4.498245142821999</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>4.758099233947855</v>
+        <v>4.498245142821999</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>4.758099233947855</v>
+        <v>4.498245142821999</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>4.758099233947855</v>
+        <v>4.498245142821999</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>0</v>
@@ -16403,20 +16336,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>4.87301138907088</v>
+        <v>4.237599016056492</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>4.87301138907088</v>
+        <v>4.237599016056492</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>4.87301138907088</v>
+        <v>4.237599016056492</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>4.87301138907088</v>
+        <v>4.237599016056492</v>
       </c>
       <c r="F62" s="3" t="n">
         <v>0</v>
@@ -16431,20 +16364,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>4.831295791859591</v>
+        <v>4.424740127395888</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>4.831295791859591</v>
+        <v>4.424740127395888</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>4.831295791859591</v>
+        <v>4.424740127395888</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>4.831295791859591</v>
+        <v>4.424740127395888</v>
       </c>
       <c r="F63" s="3" t="n">
         <v>0</v>
@@ -16459,20 +16392,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>4.559874392677332</v>
+        <v>4.758099233947855</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>4.559874392677332</v>
+        <v>4.758099233947855</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>4.559874392677332</v>
+        <v>4.758099233947855</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>4.559874392677332</v>
+        <v>4.758099233947855</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>0</v>
@@ -16487,20 +16420,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>5.057630414778758</v>
+        <v>4.87301138907088</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>5.057630414778758</v>
+        <v>4.87301138907088</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>5.057630414778758</v>
+        <v>4.87301138907088</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>5.057630414778758</v>
+        <v>4.87301138907088</v>
       </c>
       <c r="F65" s="3" t="n">
         <v>0</v>
@@ -16515,20 +16448,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>5.477189641674851</v>
+        <v>4.831295791859591</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>5.477189641674851</v>
+        <v>4.831295791859591</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>5.477189641674851</v>
+        <v>4.831295791859591</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>5.477189641674851</v>
+        <v>4.831295791859591</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>0</v>
@@ -16543,20 +16476,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>5.52972858849774</v>
+        <v>4.559874392677332</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>5.52972858849774</v>
+        <v>4.559874392677332</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>5.52972858849774</v>
+        <v>4.559874392677332</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>5.52972858849774</v>
+        <v>4.559874392677332</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -16571,20 +16504,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>5.319635559255276</v>
+        <v>5.057630414778758</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>5.319635559255276</v>
+        <v>5.057630414778758</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>5.319635559255276</v>
+        <v>5.057630414778758</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>5.319635559255276</v>
+        <v>5.057630414778758</v>
       </c>
       <c r="F68" s="3" t="n">
         <v>0</v>
@@ -16599,20 +16532,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>5.35116523759851</v>
+        <v>5.477189641674851</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>5.35116523759851</v>
+        <v>5.477189641674851</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>5.35116523759851</v>
+        <v>5.477189641674851</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>5.35116523759851</v>
+        <v>5.477189641674851</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>0</v>
@@ -16627,20 +16560,20 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>5.225222422012621</v>
+        <v>5.52972858849774</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>5.225222422012621</v>
+        <v>5.52972858849774</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>5.225222422012621</v>
+        <v>5.52972858849774</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>5.225222422012621</v>
+        <v>5.52972858849774</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>0</v>
@@ -16655,20 +16588,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>5.130500777503921</v>
+        <v>5.319635559255276</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>5.130500777503921</v>
+        <v>5.319635559255276</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>5.130500777503921</v>
+        <v>5.319635559255276</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>5.130500777503921</v>
+        <v>5.319635559255276</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>0</v>
@@ -16683,20 +16616,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>5.172368758697643</v>
+        <v>5.35116523759851</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>5.172368758697643</v>
+        <v>5.35116523759851</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>5.172368758697643</v>
+        <v>5.35116523759851</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>5.172368758697643</v>
+        <v>5.35116523759851</v>
       </c>
       <c r="F72" s="3" t="n">
         <v>0</v>
@@ -16711,20 +16644,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>4.680811347037062</v>
+        <v>5.225222422012621</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>4.680811347037062</v>
+        <v>5.225222422012621</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>4.680811347037062</v>
+        <v>5.225222422012621</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>4.680811347037062</v>
+        <v>5.225222422012621</v>
       </c>
       <c r="F73" s="3" t="n">
         <v>0</v>
@@ -16739,20 +16672,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>4.461835648432833</v>
+        <v>5.130500777503921</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>4.461835648432833</v>
+        <v>5.130500777503921</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>4.461835648432833</v>
+        <v>5.130500777503921</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>4.461835648432833</v>
+        <v>5.130500777503921</v>
       </c>
       <c r="F74" s="3" t="n">
         <v>0</v>
@@ -16767,20 +16700,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>4.264384904568952</v>
+        <v>5.172368758697643</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>4.264384904568952</v>
+        <v>5.172368758697643</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>4.264384904568952</v>
+        <v>5.172368758697643</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>4.264384904568952</v>
+        <v>5.172368758697643</v>
       </c>
       <c r="F75" s="3" t="n">
         <v>0</v>
@@ -16795,20 +16728,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>4.44135121281346</v>
+        <v>4.680811347037062</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>4.44135121281346</v>
+        <v>4.680811347037062</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>4.44135121281346</v>
+        <v>4.680811347037062</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>4.44135121281346</v>
+        <v>4.680811347037062</v>
       </c>
       <c r="F76" s="3" t="n">
         <v>0</v>
@@ -16823,20 +16756,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>3.812496961112588</v>
+        <v>4.461835648432833</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>3.812496961112588</v>
+        <v>4.461835648432833</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>3.812496961112588</v>
+        <v>4.461835648432833</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>3.812496961112588</v>
+        <v>4.461835648432833</v>
       </c>
       <c r="F77" s="3" t="n">
         <v>0</v>
@@ -16851,307 +16784,328 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>4.142846991219562</v>
+        <v>4.264384904568952</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>4.759406247070297</v>
+        <v>4.264384904568952</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>4.373166150937546</v>
+        <v>4.264384904568952</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>4.792271706483553</v>
+        <v>4.264384904568952</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.6165592558507349</v>
+        <v>0</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.2303191597179843</v>
+        <v>0</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.6494247152639909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>4.39171967147336</v>
+        <v>4.44135121281346</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>5.249294436370278</v>
+        <v>4.44135121281346</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>4.71778514034904</v>
+        <v>4.44135121281346</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>4.980916293512805</v>
+        <v>4.44135121281346</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.8575747648969179</v>
+        <v>0</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.3260654688756803</v>
+        <v>0</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.5891966220394451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>4.724906887660008</v>
+        <v>3.812496961112588</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>5.611456542936688</v>
+        <v>3.812496961112588</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>5.062685247756948</v>
+        <v>3.812496961112588</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>5.205248811719421</v>
+        <v>3.812496961112588</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.8865496552766805</v>
+        <v>0</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.3377783600969408</v>
+        <v>0</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.4803419240594131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>4.641327552554153</v>
+        <v>4.142846991219562</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>5.108953246822145</v>
+        <v>4.759406247070297</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>4.80827557603456</v>
+        <v>4.373166150937546</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>5.236553842569913</v>
+        <v>4.792271706483553</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.4676256942679924</v>
+        <v>0.6165592558507349</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.1669480234804066</v>
+        <v>0.2303191597179843</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.5952262900157601</v>
+        <v>0.6494247152639909</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>4.44302461783459</v>
+        <v>4.39171967147336</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>5.024469608744919</v>
+        <v>5.249294436370278</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>4.654371701684279</v>
+        <v>4.71778514034904</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>4.923999691256942</v>
+        <v>4.980916293512805</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.5814449909103292</v>
+        <v>0.8575747648969179</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.2113470838496889</v>
+        <v>0.3260654688756803</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.4809750734223517</v>
+        <v>0.5891966220394451</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>4.223452737068278</v>
+        <v>4.724906887660008</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>4.780929656596666</v>
+        <v>5.611456542936688</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>4.430692099619438</v>
+        <v>5.062685247756948</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>4.500631240168573</v>
+        <v>5.205248811719421</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.557476919528388</v>
+        <v>0.8865496552766805</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.2072393625511593</v>
+        <v>0.3377783600969408</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.2771785031002949</v>
+        <v>0.4803419240594131</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>4.641327552554153</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>5.108953246822145</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>4.80827557603456</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>5.236553842569913</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0.4676256942679924</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0.1669480234804066</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>0.5952262900157601</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>4.44302461783459</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>5.024469608744919</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>4.654371701684279</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>4.923999691256942</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0.5814449909103292</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0.2113470838496889</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0.4809750734223517</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>4.223452737068278</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>4.780929656596666</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>4.430692099619438</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>4.500631240168573</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0.557476919528388</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0.2072393625511593</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0.2771785031002949</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B84" s="3" t="n">
+      <c r="B87" s="3" t="n">
         <v>4.576119675071877</v>
       </c>
-      <c r="C84" s="3" t="n">
+      <c r="C87" s="3" t="n">
         <v>5.27333430542396</v>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="D87" s="3" t="n">
         <v>4.839858211590276</v>
       </c>
-      <c r="E84" s="3" t="n">
+      <c r="E87" s="3" t="n">
         <v>4.771653553462518</v>
       </c>
-      <c r="F84" s="3" t="n">
+      <c r="F87" s="3" t="n">
         <v>0.6972146303520832</v>
       </c>
-      <c r="G84" s="3" t="n">
+      <c r="G87" s="3" t="n">
         <v>0.2637385365183986</v>
       </c>
-      <c r="H84" s="3" t="n">
+      <c r="H87" s="3" t="n">
         <v>0.1955338783906413</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="1" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
         <is>
           <t>Sensibilidade à data de corte</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>O mesmo efeito, no último mês disponível, mudando só o mês em que o contrafactual começa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>corte</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>até</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>efeito contábil (p.p.)</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>efeito Bahia (p.p.)</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>efeito Salvador (p.p.)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="n">
-        <v>0.7998821623593111</v>
-      </c>
-      <c r="D91" s="3" t="n">
-        <v>0.3008129217675348</v>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>-0.003640950315886293</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="n">
-        <v>0.8346004372976612</v>
-      </c>
-      <c r="D92" s="3" t="n">
-        <v>0.313570975286348</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>-0.06206449954266891</v>
+          <t>O mesmo efeito, no último mês disponível, mudando só o mês em que o contrafactual começa.</t>
+        </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="n">
-        <v>0.7689093217567278</v>
-      </c>
-      <c r="D93" s="3" t="n">
-        <v>0.2895200110215157</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>0.0422933750593435</v>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>corte</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>até</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>efeito contábil (p.p.)</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>efeito Bahia (p.p.)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>efeito Salvador (p.p.)</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -17160,19 +17114,19 @@
         </is>
       </c>
       <c r="C94" s="3" t="n">
-        <v>0.8645159525793034</v>
+        <v>0.7998821623593111</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.3247744007882414</v>
+        <v>0.3008129217675348</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>0.1039358582213268</v>
+        <v>-0.003640950315886293</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -17181,19 +17135,19 @@
         </is>
       </c>
       <c r="C95" s="3" t="n">
-        <v>0.8670809847609817</v>
+        <v>0.8346004372976612</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.325709506093963</v>
+        <v>0.313570975286348</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>0.03689135095714668</v>
+        <v>-0.06206449954266891</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -17202,19 +17156,19 @@
         </is>
       </c>
       <c r="C96" s="3" t="n">
-        <v>0.6972146303520832</v>
+        <v>0.7689093217567278</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.2637385365183986</v>
+        <v>0.2895200110215157</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>0.1955338783906413</v>
+        <v>0.0422933750593435</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -17223,19 +17177,19 @@
         </is>
       </c>
       <c r="C97" s="3" t="n">
-        <v>0.07763066185193512</v>
+        <v>0.8645159525793034</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>0.03238953237565401</v>
+        <v>0.3247744007882414</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>-0.4537630608652865</v>
+        <v>0.1039358582213268</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -17244,33 +17198,96 @@
         </is>
       </c>
       <c r="C98" s="3" t="n">
-        <v>-0.1605560122005079</v>
+        <v>0.8670809847609817</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>-0.06270703792539134</v>
+        <v>0.325709506093963</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>-0.3924882740031777</v>
+        <v>0.03689135095714668</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>0.6972146303520832</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>0.2637385365183986</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>0.1955338783906413</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0.07763066185193512</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0.03238953237565401</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>-0.4537630608652865</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>-0.1605560122005079</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>-0.06270703792539134</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>-0.3924882740031777</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="C99" s="3" t="n">
+      <c r="C102" s="3" t="n">
         <v>-0.1864966761041753</v>
       </c>
-      <c r="D99" s="3" t="n">
+      <c r="D102" s="3" t="n">
         <v>-0.07332343078234604</v>
       </c>
-      <c r="E99" s="3" t="n">
+      <c r="E102" s="3" t="n">
         <v>-0.2828283537525733</v>
       </c>
     </row>

--- a/planilhas/ipca-defasagem.xlsx
+++ b/planilhas/ipca-defasagem.xlsx
@@ -856,7 +856,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>ATENÇÃO — a tabela mais recente da Petrobras é de 01/09/2026.</t>
+          <t>ATENÇÃO — a tabela mais recente da Petrobras é de 01/10/2026.</t>
         </is>
       </c>
     </row>
